--- a/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/20260716-contexto-relatorios-igovti-2026.xlsx
+++ b/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/20260716-contexto-relatorios-igovti-2026.xlsx
@@ -1471,7 +1471,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z2" t="n">
         <v>0.06614068918152717</v>
@@ -1507,7 +1507,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL2" t="n">
         <v>0.01637019174259785</v>
@@ -1543,7 +1543,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX2" t="n">
         <v>0.08171634449330044</v>
@@ -1597,7 +1597,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP2" t="n">
         <v>0.02511225080497755</v>
@@ -1642,7 +1642,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE2" t="n">
         <v>0.03787717275399195</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ2" t="n">
         <v>20</v>
@@ -1777,7 +1777,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX2" t="n">
         <v>0.09213674322672843</v>
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="FB2" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC2" t="n">
         <v>0.1632296302323541</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="FI2" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ2" t="n">
         <v>100</v>
@@ -2036,7 +2036,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z3" t="n">
         <v>0.06614068918152717</v>
@@ -2072,7 +2072,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL3" t="n">
         <v>0.01637019174259785</v>
@@ -2108,7 +2108,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX3" t="n">
         <v>0.08171634449330044</v>
@@ -2162,7 +2162,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP3" t="n">
         <v>0.02511225080497755</v>
@@ -2207,7 +2207,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE3" t="n">
         <v>0.03787717275399195</v>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ3" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX3" t="n">
         <v>0.09213674322672843</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="FB3" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC3" t="n">
         <v>0.1632296302323541</v>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="FI3" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ3" t="n">
         <v>100</v>
@@ -2651,7 +2651,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z4" t="n">
         <v>0.06614068918152717</v>
@@ -2687,7 +2687,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL4" t="n">
         <v>0.01637019174259785</v>
@@ -2723,7 +2723,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX4" t="n">
         <v>0.08171634449330044</v>
@@ -2777,7 +2777,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP4" t="n">
         <v>0.02511225080497755</v>
@@ -2822,7 +2822,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE4" t="n">
         <v>0.03787717275399195</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ4" t="n">
         <v>20</v>
@@ -2957,7 +2957,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX4" t="n">
         <v>0.09213674322672843</v>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="FB4" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC4" t="n">
         <v>0.1632296302323541</v>
@@ -3077,7 +3077,7 @@
         </is>
       </c>
       <c r="FI4" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ4" t="n">
         <v>100</v>
@@ -3262,7 +3262,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z5" t="n">
         <v>0.06614068918152717</v>
@@ -3298,7 +3298,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL5" t="n">
         <v>0.01637019174259785</v>
@@ -3334,7 +3334,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX5" t="n">
         <v>0.08171634449330044</v>
@@ -3388,7 +3388,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP5" t="n">
         <v>0.02511225080497755</v>
@@ -3433,7 +3433,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE5" t="n">
         <v>0.03787717275399195</v>
@@ -3448,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ5" t="n">
         <v>20</v>
@@ -3568,7 +3568,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX5" t="n">
         <v>0.09213674322672843</v>
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="FB5" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC5" t="n">
         <v>0.1632296302323541</v>
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="FI5" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ5" t="n">
         <v>100</v>
@@ -3877,7 +3877,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z6" t="n">
         <v>0.06614068918152717</v>
@@ -3913,7 +3913,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL6" t="n">
         <v>0.01637019174259785</v>
@@ -3949,7 +3949,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX6" t="n">
         <v>0.08171634449330044</v>
@@ -4003,7 +4003,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP6" t="n">
         <v>0.02511225080497755</v>
@@ -4048,7 +4048,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE6" t="n">
         <v>0.03787717275399195</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ6" t="n">
         <v>20</v>
@@ -4183,7 +4183,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX6" t="n">
         <v>0.09213674322672843</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="FB6" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC6" t="n">
         <v>0.1632296302323541</v>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="FI6" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ6" t="n">
         <v>100</v>
@@ -4492,7 +4492,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z7" t="n">
         <v>0.06614068918152717</v>
@@ -4528,7 +4528,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL7" t="n">
         <v>0.01637019174259785</v>
@@ -4564,7 +4564,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX7" t="n">
         <v>0.08171634449330044</v>
@@ -4618,7 +4618,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP7" t="n">
         <v>0.02511225080497755</v>
@@ -4663,7 +4663,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE7" t="n">
         <v>0.03787717275399195</v>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ7" t="n">
         <v>20</v>
@@ -4798,7 +4798,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX7" t="n">
         <v>0.09213674322672843</v>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="FB7" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC7" t="n">
         <v>0.1632296302323541</v>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="FI7" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ7" t="n">
         <v>100</v>
@@ -5107,7 +5107,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z8" t="n">
         <v>0.06614068918152717</v>
@@ -5143,7 +5143,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL8" t="n">
         <v>0.01637019174259785</v>
@@ -5179,7 +5179,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX8" t="n">
         <v>0.08171634449330044</v>
@@ -5233,7 +5233,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP8" t="n">
         <v>0.02511225080497755</v>
@@ -5278,7 +5278,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE8" t="n">
         <v>0.03787717275399195</v>
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ8" t="n">
         <v>20</v>
@@ -5413,7 +5413,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX8" t="n">
         <v>0.09213674322672843</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="FB8" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC8" t="n">
         <v>0.1632296302323541</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="FI8" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ8" t="n">
         <v>100</v>
@@ -5722,7 +5722,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z9" t="n">
         <v>0.06614068918152717</v>
@@ -5758,7 +5758,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL9" t="n">
         <v>0.01637019174259785</v>
@@ -5794,7 +5794,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX9" t="n">
         <v>0.08171634449330044</v>
@@ -5848,7 +5848,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP9" t="n">
         <v>0.02511225080497755</v>
@@ -5893,7 +5893,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE9" t="n">
         <v>0.03787717275399195</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ9" t="n">
         <v>20</v>
@@ -6028,7 +6028,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX9" t="n">
         <v>0.09213674322672843</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="FB9" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC9" t="n">
         <v>0.1632296302323541</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="FI9" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ9" t="n">
         <v>100</v>
@@ -6337,7 +6337,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z10" t="n">
         <v>0.06614068918152717</v>
@@ -6373,7 +6373,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL10" t="n">
         <v>0.01637019174259785</v>
@@ -6409,7 +6409,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX10" t="n">
         <v>0.08171634449330044</v>
@@ -6463,7 +6463,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP10" t="n">
         <v>0.02511225080497755</v>
@@ -6508,7 +6508,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE10" t="n">
         <v>0.03787717275399195</v>
@@ -6523,7 +6523,7 @@
         <v>0</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ10" t="n">
         <v>20</v>
@@ -6643,7 +6643,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX10" t="n">
         <v>0.09213674322672843</v>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="FB10" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC10" t="n">
         <v>0.1632296302323541</v>
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="FI10" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ10" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z11" t="n">
         <v>0.06614068918152717</v>
@@ -6988,7 +6988,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL11" t="n">
         <v>0.01637019174259785</v>
@@ -7024,7 +7024,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX11" t="n">
         <v>0.08171634449330044</v>
@@ -7078,7 +7078,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP11" t="n">
         <v>0.02511225080497755</v>
@@ -7123,7 +7123,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE11" t="n">
         <v>0.03787717275399195</v>
@@ -7138,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ11" t="n">
         <v>20</v>
@@ -7258,7 +7258,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX11" t="n">
         <v>0.09213674322672843</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="FB11" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC11" t="n">
         <v>0.1632296302323541</v>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="FI11" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ11" t="n">
         <v>100</v>
@@ -7567,7 +7567,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z12" t="n">
         <v>0.06614068918152717</v>
@@ -7603,7 +7603,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL12" t="n">
         <v>0.01637019174259785</v>
@@ -7639,7 +7639,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX12" t="n">
         <v>0.08171634449330044</v>
@@ -7693,7 +7693,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP12" t="n">
         <v>0.02511225080497755</v>
@@ -7738,7 +7738,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE12" t="n">
         <v>0.03787717275399195</v>
@@ -7753,7 +7753,7 @@
         <v>0</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ12" t="n">
         <v>20</v>
@@ -7873,7 +7873,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX12" t="n">
         <v>0.09213674322672843</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="FB12" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC12" t="n">
         <v>0.1632296302323541</v>
@@ -7993,7 +7993,7 @@
         </is>
       </c>
       <c r="FI12" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ12" t="n">
         <v>100</v>
@@ -8132,7 +8132,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z13" t="n">
         <v>0.06614068918152717</v>
@@ -8168,7 +8168,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL13" t="n">
         <v>0.01637019174259785</v>
@@ -8204,7 +8204,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX13" t="n">
         <v>0.08171634449330044</v>
@@ -8258,7 +8258,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP13" t="n">
         <v>0.02511225080497755</v>
@@ -8303,7 +8303,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE13" t="n">
         <v>0.03787717275399195</v>
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ13" t="n">
         <v>20</v>
@@ -8438,7 +8438,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX13" t="n">
         <v>0.09213674322672843</v>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="FB13" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC13" t="n">
         <v>0.1632296302323541</v>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="FI13" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ13" t="n">
         <v>100</v>
@@ -8747,7 +8747,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z14" t="n">
         <v>0.06614068918152717</v>
@@ -8783,7 +8783,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL14" t="n">
         <v>0.01637019174259785</v>
@@ -8819,7 +8819,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX14" t="n">
         <v>0.08171634449330044</v>
@@ -8873,7 +8873,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP14" t="n">
         <v>0.02511225080497755</v>
@@ -8918,7 +8918,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE14" t="n">
         <v>0.03787717275399195</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ14" t="n">
         <v>20</v>
@@ -9053,7 +9053,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX14" t="n">
         <v>0.09213674322672843</v>
@@ -9148,7 +9148,7 @@
         </is>
       </c>
       <c r="FB14" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC14" t="n">
         <v>0.1632296302323541</v>
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="FI14" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ14" t="n">
         <v>100</v>
@@ -9362,7 +9362,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z15" t="n">
         <v>0.06614068918152717</v>
@@ -9398,7 +9398,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL15" t="n">
         <v>0.01637019174259785</v>
@@ -9434,7 +9434,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX15" t="n">
         <v>0.08171634449330044</v>
@@ -9488,7 +9488,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP15" t="n">
         <v>0.02511225080497755</v>
@@ -9533,7 +9533,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE15" t="n">
         <v>0.03787717275399195</v>
@@ -9548,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ15" t="n">
         <v>20</v>
@@ -9668,7 +9668,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX15" t="n">
         <v>0.09213674322672843</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="FB15" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC15" t="n">
         <v>0.1632296302323541</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="FI15" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ15" t="n">
         <v>100</v>
@@ -9927,7 +9927,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z16" t="n">
         <v>0.06614068918152717</v>
@@ -9963,7 +9963,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL16" t="n">
         <v>0.01637019174259785</v>
@@ -9999,7 +9999,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX16" t="n">
         <v>0.08171634449330044</v>
@@ -10053,7 +10053,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP16" t="n">
         <v>0.02511225080497755</v>
@@ -10098,7 +10098,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE16" t="n">
         <v>0.03787717275399195</v>
@@ -10113,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ16" t="n">
         <v>20</v>
@@ -10233,7 +10233,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX16" t="n">
         <v>0.09213674322672843</v>
@@ -10328,7 +10328,7 @@
         </is>
       </c>
       <c r="FB16" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC16" t="n">
         <v>0.1632296302323541</v>
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="FI16" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ16" t="n">
         <v>100</v>
@@ -10542,7 +10542,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z17" t="n">
         <v>0.06614068918152717</v>
@@ -10578,7 +10578,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL17" t="n">
         <v>0.01637019174259785</v>
@@ -10614,7 +10614,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX17" t="n">
         <v>0.08171634449330044</v>
@@ -10668,7 +10668,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP17" t="n">
         <v>0.02511225080497755</v>
@@ -10713,7 +10713,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE17" t="n">
         <v>0.03787717275399195</v>
@@ -10728,7 +10728,7 @@
         <v>0</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ17" t="n">
         <v>20</v>
@@ -10848,7 +10848,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX17" t="n">
         <v>0.09213674322672843</v>
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="FB17" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC17" t="n">
         <v>0.1632296302323541</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="FI17" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ17" t="n">
         <v>100</v>
@@ -11107,7 +11107,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z18" t="n">
         <v>0.06614068918152717</v>
@@ -11143,7 +11143,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL18" t="n">
         <v>0.01637019174259785</v>
@@ -11179,7 +11179,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX18" t="n">
         <v>0.08171634449330044</v>
@@ -11233,7 +11233,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP18" t="n">
         <v>0.02511225080497755</v>
@@ -11278,7 +11278,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE18" t="n">
         <v>0.03787717275399195</v>
@@ -11293,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ18" t="n">
         <v>20</v>
@@ -11413,7 +11413,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX18" t="n">
         <v>0.09213674322672843</v>
@@ -11508,7 +11508,7 @@
         </is>
       </c>
       <c r="FB18" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC18" t="n">
         <v>0.1632296302323541</v>
@@ -11533,7 +11533,7 @@
         </is>
       </c>
       <c r="FI18" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ18" t="n">
         <v>100</v>
@@ -11722,7 +11722,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z19" t="n">
         <v>0.06614068918152717</v>
@@ -11758,7 +11758,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL19" t="n">
         <v>0.01637019174259785</v>
@@ -11794,7 +11794,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX19" t="n">
         <v>0.08171634449330044</v>
@@ -11848,7 +11848,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP19" t="n">
         <v>0.02511225080497755</v>
@@ -11893,7 +11893,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE19" t="n">
         <v>0.03787717275399195</v>
@@ -11908,7 +11908,7 @@
         <v>0</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ19" t="n">
         <v>20</v>
@@ -12028,7 +12028,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX19" t="n">
         <v>0.09213674322672843</v>
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="FB19" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC19" t="n">
         <v>0.1632296302323541</v>
@@ -12148,7 +12148,7 @@
         </is>
       </c>
       <c r="FI19" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ19" t="n">
         <v>100</v>
@@ -12287,7 +12287,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z20" t="n">
         <v>0.06614068918152717</v>
@@ -12323,7 +12323,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL20" t="n">
         <v>0.01637019174259785</v>
@@ -12359,7 +12359,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX20" t="n">
         <v>0.08171634449330044</v>
@@ -12413,7 +12413,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO20" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP20" t="n">
         <v>0.02511225080497755</v>
@@ -12458,7 +12458,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE20" t="n">
         <v>0.03787717275399195</v>
@@ -12473,7 +12473,7 @@
         <v>0</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ20" t="n">
         <v>20</v>
@@ -12593,7 +12593,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW20" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX20" t="n">
         <v>0.09213674322672843</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="FB20" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC20" t="n">
         <v>0.1632296302323541</v>
@@ -12713,7 +12713,7 @@
         </is>
       </c>
       <c r="FI20" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ20" t="n">
         <v>100</v>
@@ -12852,7 +12852,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z21" t="n">
         <v>0.06614068918152717</v>
@@ -12888,7 +12888,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL21" t="n">
         <v>0.01637019174259785</v>
@@ -12924,7 +12924,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX21" t="n">
         <v>0.08171634449330044</v>
@@ -12978,7 +12978,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO21" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP21" t="n">
         <v>0.02511225080497755</v>
@@ -13023,7 +13023,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD21" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE21" t="n">
         <v>0.03787717275399195</v>
@@ -13038,7 +13038,7 @@
         <v>0</v>
       </c>
       <c r="CI21" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ21" t="n">
         <v>20</v>
@@ -13158,7 +13158,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW21" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX21" t="n">
         <v>0.09213674322672843</v>
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="FB21" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC21" t="n">
         <v>0.1632296302323541</v>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="FI21" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ21" t="n">
         <v>100</v>
@@ -13467,7 +13467,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z22" t="n">
         <v>0.06614068918152717</v>
@@ -13503,7 +13503,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL22" t="n">
         <v>0.01637019174259785</v>
@@ -13539,7 +13539,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX22" t="n">
         <v>0.08171634449330044</v>
@@ -13593,7 +13593,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO22" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP22" t="n">
         <v>0.02511225080497755</v>
@@ -13638,7 +13638,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE22" t="n">
         <v>0.03787717275399195</v>
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ22" t="n">
         <v>20</v>
@@ -13773,7 +13773,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW22" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX22" t="n">
         <v>0.09213674322672843</v>
@@ -13868,7 +13868,7 @@
         </is>
       </c>
       <c r="FB22" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC22" t="n">
         <v>0.1632296302323541</v>
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="FI22" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ22" t="n">
         <v>100</v>
@@ -14032,7 +14032,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z23" t="n">
         <v>0.06614068918152717</v>
@@ -14068,7 +14068,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL23" t="n">
         <v>0.01637019174259785</v>
@@ -14104,7 +14104,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX23" t="n">
         <v>0.08171634449330044</v>
@@ -14158,7 +14158,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP23" t="n">
         <v>0.02511225080497755</v>
@@ -14203,7 +14203,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD23" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE23" t="n">
         <v>0.03787717275399195</v>
@@ -14218,7 +14218,7 @@
         <v>0</v>
       </c>
       <c r="CI23" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ23" t="n">
         <v>20</v>
@@ -14338,7 +14338,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW23" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX23" t="n">
         <v>0.09213674322672843</v>
@@ -14433,7 +14433,7 @@
         </is>
       </c>
       <c r="FB23" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC23" t="n">
         <v>0.1632296302323541</v>
@@ -14458,7 +14458,7 @@
         </is>
       </c>
       <c r="FI23" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ23" t="n">
         <v>100</v>
@@ -14647,7 +14647,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z24" t="n">
         <v>0.06614068918152717</v>
@@ -14683,7 +14683,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL24" t="n">
         <v>0.01637019174259785</v>
@@ -14719,7 +14719,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX24" t="n">
         <v>0.08171634449330044</v>
@@ -14773,7 +14773,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO24" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP24" t="n">
         <v>0.02511225080497755</v>
@@ -14818,7 +14818,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE24" t="n">
         <v>0.03787717275399195</v>
@@ -14833,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ24" t="n">
         <v>20</v>
@@ -14953,7 +14953,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW24" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX24" t="n">
         <v>0.09213674322672843</v>
@@ -15048,7 +15048,7 @@
         </is>
       </c>
       <c r="FB24" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC24" t="n">
         <v>0.1632296302323541</v>
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="FI24" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ24" t="n">
         <v>100</v>
@@ -15262,7 +15262,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z25" t="n">
         <v>0.06614068918152717</v>
@@ -15298,7 +15298,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL25" t="n">
         <v>0.01637019174259785</v>
@@ -15334,7 +15334,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX25" t="n">
         <v>0.08171634449330044</v>
@@ -15388,7 +15388,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO25" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP25" t="n">
         <v>0.02511225080497755</v>
@@ -15433,7 +15433,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE25" t="n">
         <v>0.03787717275399195</v>
@@ -15448,7 +15448,7 @@
         <v>0</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ25" t="n">
         <v>20</v>
@@ -15568,7 +15568,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW25" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX25" t="n">
         <v>0.09213674322672843</v>
@@ -15663,7 +15663,7 @@
         </is>
       </c>
       <c r="FB25" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC25" t="n">
         <v>0.1632296302323541</v>
@@ -15688,7 +15688,7 @@
         </is>
       </c>
       <c r="FI25" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ25" t="n">
         <v>100</v>
@@ -15806,7 +15806,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4793019068684717</v>
+        <v>0.4940729802266843</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4888332462462698</v>
+        <v>0.5197547195378435</v>
       </c>
       <c r="E26" t="n">
         <v>0.8307633054738472</v>
@@ -15877,7 +15877,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z26" t="n">
         <v>0.06614068918152717</v>
@@ -15913,7 +15913,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL26" t="n">
         <v>0.01637019174259785</v>
@@ -15949,7 +15949,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX26" t="n">
         <v>0.08171634449330044</v>
@@ -16003,7 +16003,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP26" t="n">
         <v>0.02511225080497755</v>
@@ -16048,7 +16048,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD26" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE26" t="n">
         <v>0.03787717275399195</v>
@@ -16063,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="CI26" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ26" t="n">
         <v>20</v>
@@ -16183,7 +16183,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW26" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX26" t="n">
         <v>0.09213674322672843</v>
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="FB26" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC26" t="n">
         <v>0.1632296302323541</v>
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="FI26" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ26" t="n">
         <v>100</v>
@@ -16375,10 +16375,10 @@
         <v>0.6777257448181767</v>
       </c>
       <c r="GC26" t="n">
-        <v>0.5368334965420798</v>
+        <v>0.5530063887842832</v>
       </c>
       <c r="GD26" t="n">
-        <v>-0.1408922482760969</v>
+        <v>-0.1247193560338935</v>
       </c>
       <c r="GE26" t="inlineStr">
         <is>
@@ -16389,10 +16389,10 @@
         <v>0.7014689449943675</v>
       </c>
       <c r="GG26" t="n">
-        <v>0.5794529442739249</v>
+        <v>0.6117987287583319</v>
       </c>
       <c r="GH26" t="n">
-        <v>-0.1220160007204426</v>
+        <v>-0.08967021623603566</v>
       </c>
       <c r="GI26" t="n">
         <v>0.6539825446419859</v>
@@ -16492,7 +16492,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z27" t="n">
         <v>0.06614068918152717</v>
@@ -16528,7 +16528,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL27" t="n">
         <v>0.01637019174259785</v>
@@ -16564,7 +16564,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX27" t="n">
         <v>0.08171634449330044</v>
@@ -16618,7 +16618,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO27" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP27" t="n">
         <v>0.02511225080497755</v>
@@ -16663,7 +16663,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD27" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE27" t="n">
         <v>0.03787717275399195</v>
@@ -16678,7 +16678,7 @@
         <v>0</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ27" t="n">
         <v>20</v>
@@ -16798,7 +16798,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW27" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX27" t="n">
         <v>0.09213674322672843</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="FB27" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC27" t="n">
         <v>0.1632296302323541</v>
@@ -16918,7 +16918,7 @@
         </is>
       </c>
       <c r="FI27" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ27" t="n">
         <v>100</v>
@@ -17103,7 +17103,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z28" t="n">
         <v>0.06614068918152717</v>
@@ -17139,7 +17139,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL28" t="n">
         <v>0.01637019174259785</v>
@@ -17175,7 +17175,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX28" t="n">
         <v>0.08171634449330044</v>
@@ -17229,7 +17229,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP28" t="n">
         <v>0.02511225080497755</v>
@@ -17274,7 +17274,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE28" t="n">
         <v>0.03787717275399195</v>
@@ -17289,7 +17289,7 @@
         <v>0</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ28" t="n">
         <v>20</v>
@@ -17409,7 +17409,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW28" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX28" t="n">
         <v>0.09213674322672843</v>
@@ -17504,7 +17504,7 @@
         </is>
       </c>
       <c r="FB28" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC28" t="n">
         <v>0.1632296302323541</v>
@@ -17529,7 +17529,7 @@
         </is>
       </c>
       <c r="FI28" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ28" t="n">
         <v>100</v>
@@ -17718,7 +17718,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z29" t="n">
         <v>0.06614068918152717</v>
@@ -17754,7 +17754,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL29" t="n">
         <v>0.01637019174259785</v>
@@ -17790,7 +17790,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX29" t="n">
         <v>0.08171634449330044</v>
@@ -17844,7 +17844,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO29" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP29" t="n">
         <v>0.02511225080497755</v>
@@ -17889,7 +17889,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD29" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE29" t="n">
         <v>0.03787717275399195</v>
@@ -17904,7 +17904,7 @@
         <v>0</v>
       </c>
       <c r="CI29" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ29" t="n">
         <v>20</v>
@@ -18024,7 +18024,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW29" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX29" t="n">
         <v>0.09213674322672843</v>
@@ -18119,7 +18119,7 @@
         </is>
       </c>
       <c r="FB29" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC29" t="n">
         <v>0.1632296302323541</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="FI29" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ29" t="n">
         <v>100</v>
@@ -18333,7 +18333,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z30" t="n">
         <v>0.06614068918152717</v>
@@ -18369,7 +18369,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL30" t="n">
         <v>0.01637019174259785</v>
@@ -18405,7 +18405,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX30" t="n">
         <v>0.08171634449330044</v>
@@ -18459,7 +18459,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO30" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP30" t="n">
         <v>0.02511225080497755</v>
@@ -18504,7 +18504,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE30" t="n">
         <v>0.03787717275399195</v>
@@ -18519,7 +18519,7 @@
         <v>0</v>
       </c>
       <c r="CI30" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ30" t="n">
         <v>20</v>
@@ -18639,7 +18639,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW30" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX30" t="n">
         <v>0.09213674322672843</v>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="FB30" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC30" t="n">
         <v>0.1632296302323541</v>
@@ -18759,7 +18759,7 @@
         </is>
       </c>
       <c r="FI30" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ30" t="n">
         <v>100</v>
@@ -18898,7 +18898,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z31" t="n">
         <v>0.06614068918152717</v>
@@ -18934,7 +18934,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL31" t="n">
         <v>0.01637019174259785</v>
@@ -18970,7 +18970,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX31" t="n">
         <v>0.08171634449330044</v>
@@ -19024,7 +19024,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO31" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP31" t="n">
         <v>0.02511225080497755</v>
@@ -19069,7 +19069,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE31" t="n">
         <v>0.03787717275399195</v>
@@ -19084,7 +19084,7 @@
         <v>0</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ31" t="n">
         <v>20</v>
@@ -19204,7 +19204,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW31" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX31" t="n">
         <v>0.09213674322672843</v>
@@ -19299,7 +19299,7 @@
         </is>
       </c>
       <c r="FB31" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC31" t="n">
         <v>0.1632296302323541</v>
@@ -19324,7 +19324,7 @@
         </is>
       </c>
       <c r="FI31" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ31" t="n">
         <v>100</v>
@@ -19513,7 +19513,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z32" t="n">
         <v>0.06614068918152717</v>
@@ -19549,7 +19549,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL32" t="n">
         <v>0.01637019174259785</v>
@@ -19585,7 +19585,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX32" t="n">
         <v>0.08171634449330044</v>
@@ -19639,7 +19639,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO32" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP32" t="n">
         <v>0.02511225080497755</v>
@@ -19684,7 +19684,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD32" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE32" t="n">
         <v>0.03787717275399195</v>
@@ -19699,7 +19699,7 @@
         <v>0</v>
       </c>
       <c r="CI32" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ32" t="n">
         <v>20</v>
@@ -19819,7 +19819,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW32" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX32" t="n">
         <v>0.09213674322672843</v>
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="FB32" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC32" t="n">
         <v>0.1632296302323541</v>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="FI32" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ32" t="n">
         <v>100</v>
@@ -20078,7 +20078,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z33" t="n">
         <v>0.06614068918152717</v>
@@ -20114,7 +20114,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL33" t="n">
         <v>0.01637019174259785</v>
@@ -20150,7 +20150,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX33" t="n">
         <v>0.08171634449330044</v>
@@ -20204,7 +20204,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO33" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP33" t="n">
         <v>0.02511225080497755</v>
@@ -20249,7 +20249,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD33" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE33" t="n">
         <v>0.03787717275399195</v>
@@ -20264,7 +20264,7 @@
         <v>0</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ33" t="n">
         <v>20</v>
@@ -20384,7 +20384,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW33" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX33" t="n">
         <v>0.09213674322672843</v>
@@ -20479,7 +20479,7 @@
         </is>
       </c>
       <c r="FB33" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC33" t="n">
         <v>0.1632296302323541</v>
@@ -20504,7 +20504,7 @@
         </is>
       </c>
       <c r="FI33" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ33" t="n">
         <v>100</v>
@@ -20643,7 +20643,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z34" t="n">
         <v>0.06614068918152717</v>
@@ -20679,7 +20679,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL34" t="n">
         <v>0.01637019174259785</v>
@@ -20715,7 +20715,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX34" t="n">
         <v>0.08171634449330044</v>
@@ -20769,7 +20769,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO34" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP34" t="n">
         <v>0.02511225080497755</v>
@@ -20814,7 +20814,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE34" t="n">
         <v>0.03787717275399195</v>
@@ -20829,7 +20829,7 @@
         <v>0</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ34" t="n">
         <v>20</v>
@@ -20949,7 +20949,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW34" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX34" t="n">
         <v>0.09213674322672843</v>
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="FB34" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC34" t="n">
         <v>0.1632296302323541</v>
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="FI34" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ34" t="n">
         <v>100</v>
@@ -21208,7 +21208,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z35" t="n">
         <v>0.06614068918152717</v>
@@ -21244,7 +21244,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL35" t="n">
         <v>0.01637019174259785</v>
@@ -21280,7 +21280,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX35" t="n">
         <v>0.08171634449330044</v>
@@ -21334,7 +21334,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO35" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP35" t="n">
         <v>0.02511225080497755</v>
@@ -21379,7 +21379,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD35" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE35" t="n">
         <v>0.03787717275399195</v>
@@ -21394,7 +21394,7 @@
         <v>0</v>
       </c>
       <c r="CI35" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ35" t="n">
         <v>20</v>
@@ -21514,7 +21514,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW35" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX35" t="n">
         <v>0.09213674322672843</v>
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="FB35" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC35" t="n">
         <v>0.1632296302323541</v>
@@ -21634,7 +21634,7 @@
         </is>
       </c>
       <c r="FI35" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ35" t="n">
         <v>100</v>
@@ -21773,7 +21773,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z36" t="n">
         <v>0.06614068918152717</v>
@@ -21809,7 +21809,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL36" t="n">
         <v>0.01637019174259785</v>
@@ -21845,7 +21845,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX36" t="n">
         <v>0.08171634449330044</v>
@@ -21899,7 +21899,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO36" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP36" t="n">
         <v>0.02511225080497755</v>
@@ -21944,7 +21944,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD36" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE36" t="n">
         <v>0.03787717275399195</v>
@@ -21959,7 +21959,7 @@
         <v>0</v>
       </c>
       <c r="CI36" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ36" t="n">
         <v>20</v>
@@ -22079,7 +22079,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW36" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX36" t="n">
         <v>0.09213674322672843</v>
@@ -22174,7 +22174,7 @@
         </is>
       </c>
       <c r="FB36" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC36" t="n">
         <v>0.1632296302323541</v>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="FI36" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ36" t="n">
         <v>100</v>
@@ -22338,7 +22338,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z37" t="n">
         <v>0.06614068918152717</v>
@@ -22374,7 +22374,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL37" t="n">
         <v>0.01637019174259785</v>
@@ -22410,7 +22410,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX37" t="n">
         <v>0.08171634449330044</v>
@@ -22464,7 +22464,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO37" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP37" t="n">
         <v>0.02511225080497755</v>
@@ -22509,7 +22509,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD37" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE37" t="n">
         <v>0.03787717275399195</v>
@@ -22524,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ37" t="n">
         <v>20</v>
@@ -22644,7 +22644,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW37" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX37" t="n">
         <v>0.09213674322672843</v>
@@ -22739,7 +22739,7 @@
         </is>
       </c>
       <c r="FB37" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC37" t="n">
         <v>0.1632296302323541</v>
@@ -22764,7 +22764,7 @@
         </is>
       </c>
       <c r="FI37" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ37" t="n">
         <v>100</v>
@@ -22953,7 +22953,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z38" t="n">
         <v>0.06614068918152717</v>
@@ -22989,7 +22989,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL38" t="n">
         <v>0.01637019174259785</v>
@@ -23025,7 +23025,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX38" t="n">
         <v>0.08171634449330044</v>
@@ -23079,7 +23079,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO38" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP38" t="n">
         <v>0.02511225080497755</v>
@@ -23124,7 +23124,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD38" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE38" t="n">
         <v>0.03787717275399195</v>
@@ -23139,7 +23139,7 @@
         <v>0</v>
       </c>
       <c r="CI38" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ38" t="n">
         <v>20</v>
@@ -23259,7 +23259,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW38" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX38" t="n">
         <v>0.09213674322672843</v>
@@ -23354,7 +23354,7 @@
         </is>
       </c>
       <c r="FB38" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC38" t="n">
         <v>0.1632296302323541</v>
@@ -23379,7 +23379,7 @@
         </is>
       </c>
       <c r="FI38" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ38" t="n">
         <v>100</v>
@@ -23568,7 +23568,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z39" t="n">
         <v>0.06614068918152717</v>
@@ -23604,7 +23604,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL39" t="n">
         <v>0.01637019174259785</v>
@@ -23640,7 +23640,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX39" t="n">
         <v>0.08171634449330044</v>
@@ -23694,7 +23694,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO39" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP39" t="n">
         <v>0.02511225080497755</v>
@@ -23739,7 +23739,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE39" t="n">
         <v>0.03787717275399195</v>
@@ -23754,7 +23754,7 @@
         <v>0</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ39" t="n">
         <v>20</v>
@@ -23874,7 +23874,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW39" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX39" t="n">
         <v>0.09213674322672843</v>
@@ -23969,7 +23969,7 @@
         </is>
       </c>
       <c r="FB39" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC39" t="n">
         <v>0.1632296302323541</v>
@@ -23994,7 +23994,7 @@
         </is>
       </c>
       <c r="FI39" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ39" t="n">
         <v>100</v>
@@ -24133,7 +24133,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z40" t="n">
         <v>0.06614068918152717</v>
@@ -24169,7 +24169,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL40" t="n">
         <v>0.01637019174259785</v>
@@ -24205,7 +24205,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX40" t="n">
         <v>0.08171634449330044</v>
@@ -24259,7 +24259,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO40" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP40" t="n">
         <v>0.02511225080497755</v>
@@ -24304,7 +24304,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE40" t="n">
         <v>0.03787717275399195</v>
@@ -24319,7 +24319,7 @@
         <v>0</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ40" t="n">
         <v>20</v>
@@ -24439,7 +24439,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW40" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX40" t="n">
         <v>0.09213674322672843</v>
@@ -24534,7 +24534,7 @@
         </is>
       </c>
       <c r="FB40" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC40" t="n">
         <v>0.1632296302323541</v>
@@ -24559,7 +24559,7 @@
         </is>
       </c>
       <c r="FI40" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ40" t="n">
         <v>100</v>
@@ -24748,7 +24748,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z41" t="n">
         <v>0.06614068918152717</v>
@@ -24784,7 +24784,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL41" t="n">
         <v>0.01637019174259785</v>
@@ -24820,7 +24820,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX41" t="n">
         <v>0.08171634449330044</v>
@@ -24874,7 +24874,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO41" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP41" t="n">
         <v>0.02511225080497755</v>
@@ -24919,7 +24919,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD41" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE41" t="n">
         <v>0.03787717275399195</v>
@@ -24934,7 +24934,7 @@
         <v>0</v>
       </c>
       <c r="CI41" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ41" t="n">
         <v>20</v>
@@ -25054,7 +25054,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW41" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX41" t="n">
         <v>0.09213674322672843</v>
@@ -25149,7 +25149,7 @@
         </is>
       </c>
       <c r="FB41" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC41" t="n">
         <v>0.1632296302323541</v>
@@ -25174,7 +25174,7 @@
         </is>
       </c>
       <c r="FI41" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ41" t="n">
         <v>100</v>
@@ -25313,7 +25313,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z42" t="n">
         <v>0.06614068918152717</v>
@@ -25349,7 +25349,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL42" t="n">
         <v>0.01637019174259785</v>
@@ -25385,7 +25385,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX42" t="n">
         <v>0.08171634449330044</v>
@@ -25439,7 +25439,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO42" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP42" t="n">
         <v>0.02511225080497755</v>
@@ -25484,7 +25484,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD42" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE42" t="n">
         <v>0.03787717275399195</v>
@@ -25499,7 +25499,7 @@
         <v>0</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ42" t="n">
         <v>20</v>
@@ -25619,7 +25619,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW42" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX42" t="n">
         <v>0.09213674322672843</v>
@@ -25714,7 +25714,7 @@
         </is>
       </c>
       <c r="FB42" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC42" t="n">
         <v>0.1632296302323541</v>
@@ -25739,7 +25739,7 @@
         </is>
       </c>
       <c r="FI42" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ42" t="n">
         <v>100</v>
@@ -25857,7 +25857,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.751109300909877</v>
+        <v>0.7545689962328395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>0.9153816527369236</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5226429139054795</v>
+        <v>0.5584157992842496</v>
       </c>
       <c r="G43" t="n">
         <v>0.5693195218228373</v>
@@ -25892,7 +25892,7 @@
         <v>0.6265290557486204</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6465796400543724</v>
+        <v>0.6532035550637455</v>
       </c>
       <c r="N43" t="n">
         <v>113</v>
@@ -25928,7 +25928,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z43" t="n">
         <v>0.06614068918152717</v>
@@ -25964,7 +25964,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL43" t="n">
         <v>0.01637019174259785</v>
@@ -26000,7 +26000,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX43" t="n">
         <v>0.08171634449330044</v>
@@ -26054,7 +26054,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO43" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP43" t="n">
         <v>0.02511225080497755</v>
@@ -26099,7 +26099,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE43" t="n">
         <v>0.03787717275399195</v>
@@ -26114,7 +26114,7 @@
         <v>0</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ43" t="n">
         <v>20</v>
@@ -26234,7 +26234,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW43" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX43" t="n">
         <v>0.09213674322672843</v>
@@ -26329,7 +26329,7 @@
         </is>
       </c>
       <c r="FB43" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC43" t="n">
         <v>0.1632296302323541</v>
@@ -26354,7 +26354,7 @@
         </is>
       </c>
       <c r="FI43" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ43" t="n">
         <v>100</v>
@@ -26426,10 +26426,10 @@
         <v>0.4092267544642821</v>
       </c>
       <c r="GC43" t="n">
-        <v>0.6619023815575781</v>
+        <v>0.6636765201862554</v>
       </c>
       <c r="GD43" t="n">
-        <v>0.2526756270932959</v>
+        <v>0.2544497657219733</v>
       </c>
       <c r="GE43" t="inlineStr">
         <is>
@@ -26449,10 +26449,10 @@
         <v>0.2773565164913028</v>
       </c>
       <c r="GJ43" t="n">
-        <v>0.4871434185024624</v>
+        <v>0.4906916957598171</v>
       </c>
       <c r="GK43" t="n">
-        <v>0.2097869020111596</v>
+        <v>0.2133351792685143</v>
       </c>
       <c r="GL43" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z44" t="n">
         <v>0.06614068918152717</v>
@@ -26579,7 +26579,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL44" t="n">
         <v>0.01637019174259785</v>
@@ -26615,7 +26615,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX44" t="n">
         <v>0.08171634449330044</v>
@@ -26669,7 +26669,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO44" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP44" t="n">
         <v>0.02511225080497755</v>
@@ -26714,7 +26714,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE44" t="n">
         <v>0.03787717275399195</v>
@@ -26729,7 +26729,7 @@
         <v>0</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ44" t="n">
         <v>20</v>
@@ -26849,7 +26849,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW44" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX44" t="n">
         <v>0.09213674322672843</v>
@@ -26944,7 +26944,7 @@
         </is>
       </c>
       <c r="FB44" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC44" t="n">
         <v>0.1632296302323541</v>
@@ -26969,7 +26969,7 @@
         </is>
       </c>
       <c r="FI44" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ44" t="n">
         <v>100</v>
@@ -27108,7 +27108,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z45" t="n">
         <v>0.06614068918152717</v>
@@ -27144,7 +27144,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL45" t="n">
         <v>0.01637019174259785</v>
@@ -27180,7 +27180,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX45" t="n">
         <v>0.08171634449330044</v>
@@ -27234,7 +27234,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO45" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP45" t="n">
         <v>0.02511225080497755</v>
@@ -27279,7 +27279,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD45" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE45" t="n">
         <v>0.03787717275399195</v>
@@ -27294,7 +27294,7 @@
         <v>0</v>
       </c>
       <c r="CI45" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ45" t="n">
         <v>20</v>
@@ -27414,7 +27414,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW45" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX45" t="n">
         <v>0.09213674322672843</v>
@@ -27509,7 +27509,7 @@
         </is>
       </c>
       <c r="FB45" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC45" t="n">
         <v>0.1632296302323541</v>
@@ -27534,7 +27534,7 @@
         </is>
       </c>
       <c r="FI45" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ45" t="n">
         <v>100</v>
@@ -27723,7 +27723,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z46" t="n">
         <v>0.06614068918152717</v>
@@ -27759,7 +27759,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL46" t="n">
         <v>0.01637019174259785</v>
@@ -27795,7 +27795,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX46" t="n">
         <v>0.08171634449330044</v>
@@ -27849,7 +27849,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO46" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP46" t="n">
         <v>0.02511225080497755</v>
@@ -27894,7 +27894,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE46" t="n">
         <v>0.03787717275399195</v>
@@ -27909,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ46" t="n">
         <v>20</v>
@@ -28029,7 +28029,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW46" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX46" t="n">
         <v>0.09213674322672843</v>
@@ -28124,7 +28124,7 @@
         </is>
       </c>
       <c r="FB46" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC46" t="n">
         <v>0.1632296302323541</v>
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="FI46" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ46" t="n">
         <v>100</v>
@@ -28338,7 +28338,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z47" t="n">
         <v>0.06614068918152717</v>
@@ -28374,7 +28374,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL47" t="n">
         <v>0.01637019174259785</v>
@@ -28410,7 +28410,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX47" t="n">
         <v>0.08171634449330044</v>
@@ -28464,7 +28464,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO47" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP47" t="n">
         <v>0.02511225080497755</v>
@@ -28509,7 +28509,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD47" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE47" t="n">
         <v>0.03787717275399195</v>
@@ -28524,7 +28524,7 @@
         <v>0</v>
       </c>
       <c r="CI47" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ47" t="n">
         <v>20</v>
@@ -28644,7 +28644,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW47" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX47" t="n">
         <v>0.09213674322672843</v>
@@ -28739,7 +28739,7 @@
         </is>
       </c>
       <c r="FB47" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC47" t="n">
         <v>0.1632296302323541</v>
@@ -28764,7 +28764,7 @@
         </is>
       </c>
       <c r="FI47" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ47" t="n">
         <v>100</v>
@@ -28903,7 +28903,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z48" t="n">
         <v>0.06614068918152717</v>
@@ -28939,7 +28939,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL48" t="n">
         <v>0.01637019174259785</v>
@@ -28975,7 +28975,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX48" t="n">
         <v>0.08171634449330044</v>
@@ -29029,7 +29029,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO48" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP48" t="n">
         <v>0.02511225080497755</v>
@@ -29074,7 +29074,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD48" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE48" t="n">
         <v>0.03787717275399195</v>
@@ -29089,7 +29089,7 @@
         <v>0</v>
       </c>
       <c r="CI48" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ48" t="n">
         <v>20</v>
@@ -29209,7 +29209,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW48" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX48" t="n">
         <v>0.09213674322672843</v>
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="FB48" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC48" t="n">
         <v>0.1632296302323541</v>
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="FI48" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ48" t="n">
         <v>100</v>
@@ -29518,7 +29518,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z49" t="n">
         <v>0.06614068918152717</v>
@@ -29554,7 +29554,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL49" t="n">
         <v>0.01637019174259785</v>
@@ -29590,7 +29590,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX49" t="n">
         <v>0.08171634449330044</v>
@@ -29644,7 +29644,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO49" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP49" t="n">
         <v>0.02511225080497755</v>
@@ -29689,7 +29689,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE49" t="n">
         <v>0.03787717275399195</v>
@@ -29704,7 +29704,7 @@
         <v>0</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ49" t="n">
         <v>20</v>
@@ -29824,7 +29824,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW49" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX49" t="n">
         <v>0.09213674322672843</v>
@@ -29919,7 +29919,7 @@
         </is>
       </c>
       <c r="FB49" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC49" t="n">
         <v>0.1632296302323541</v>
@@ -29944,7 +29944,7 @@
         </is>
       </c>
       <c r="FI49" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ49" t="n">
         <v>100</v>
@@ -30083,7 +30083,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z50" t="n">
         <v>0.06614068918152717</v>
@@ -30119,7 +30119,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL50" t="n">
         <v>0.01637019174259785</v>
@@ -30155,7 +30155,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX50" t="n">
         <v>0.08171634449330044</v>
@@ -30209,7 +30209,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO50" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP50" t="n">
         <v>0.02511225080497755</v>
@@ -30254,7 +30254,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD50" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE50" t="n">
         <v>0.03787717275399195</v>
@@ -30269,7 +30269,7 @@
         <v>0</v>
       </c>
       <c r="CI50" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ50" t="n">
         <v>20</v>
@@ -30389,7 +30389,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW50" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX50" t="n">
         <v>0.09213674322672843</v>
@@ -30484,7 +30484,7 @@
         </is>
       </c>
       <c r="FB50" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC50" t="n">
         <v>0.1632296302323541</v>
@@ -30509,7 +30509,7 @@
         </is>
       </c>
       <c r="FI50" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ50" t="n">
         <v>100</v>
@@ -30698,7 +30698,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z51" t="n">
         <v>0.06614068918152717</v>
@@ -30734,7 +30734,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL51" t="n">
         <v>0.01637019174259785</v>
@@ -30770,7 +30770,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX51" t="n">
         <v>0.08171634449330044</v>
@@ -30824,7 +30824,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO51" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP51" t="n">
         <v>0.02511225080497755</v>
@@ -30869,7 +30869,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD51" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE51" t="n">
         <v>0.03787717275399195</v>
@@ -30884,7 +30884,7 @@
         <v>0</v>
       </c>
       <c r="CI51" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ51" t="n">
         <v>20</v>
@@ -31004,7 +31004,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW51" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX51" t="n">
         <v>0.09213674322672843</v>
@@ -31099,7 +31099,7 @@
         </is>
       </c>
       <c r="FB51" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC51" t="n">
         <v>0.1632296302323541</v>
@@ -31124,7 +31124,7 @@
         </is>
       </c>
       <c r="FI51" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ51" t="n">
         <v>100</v>
@@ -31313,7 +31313,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z52" t="n">
         <v>0.06614068918152717</v>
@@ -31349,7 +31349,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL52" t="n">
         <v>0.01637019174259785</v>
@@ -31385,7 +31385,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX52" t="n">
         <v>0.08171634449330044</v>
@@ -31439,7 +31439,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO52" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP52" t="n">
         <v>0.02511225080497755</v>
@@ -31484,7 +31484,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE52" t="n">
         <v>0.03787717275399195</v>
@@ -31499,7 +31499,7 @@
         <v>0</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ52" t="n">
         <v>20</v>
@@ -31619,7 +31619,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW52" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX52" t="n">
         <v>0.09213674322672843</v>
@@ -31714,7 +31714,7 @@
         </is>
       </c>
       <c r="FB52" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC52" t="n">
         <v>0.1632296302323541</v>
@@ -31739,7 +31739,7 @@
         </is>
       </c>
       <c r="FI52" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ52" t="n">
         <v>100</v>
@@ -31878,7 +31878,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z53" t="n">
         <v>0.06614068918152717</v>
@@ -31914,7 +31914,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL53" t="n">
         <v>0.01637019174259785</v>
@@ -31950,7 +31950,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX53" t="n">
         <v>0.08171634449330044</v>
@@ -32004,7 +32004,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO53" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP53" t="n">
         <v>0.02511225080497755</v>
@@ -32049,7 +32049,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD53" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE53" t="n">
         <v>0.03787717275399195</v>
@@ -32064,7 +32064,7 @@
         <v>0</v>
       </c>
       <c r="CI53" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ53" t="n">
         <v>20</v>
@@ -32184,7 +32184,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW53" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX53" t="n">
         <v>0.09213674322672843</v>
@@ -32279,7 +32279,7 @@
         </is>
       </c>
       <c r="FB53" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC53" t="n">
         <v>0.1632296302323541</v>
@@ -32304,7 +32304,7 @@
         </is>
       </c>
       <c r="FI53" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ53" t="n">
         <v>100</v>
@@ -32493,7 +32493,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z54" t="n">
         <v>0.06614068918152717</v>
@@ -32529,7 +32529,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL54" t="n">
         <v>0.01637019174259785</v>
@@ -32565,7 +32565,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX54" t="n">
         <v>0.08171634449330044</v>
@@ -32619,7 +32619,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO54" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP54" t="n">
         <v>0.02511225080497755</v>
@@ -32664,7 +32664,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD54" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE54" t="n">
         <v>0.03787717275399195</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="CI54" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ54" t="n">
         <v>20</v>
@@ -32799,7 +32799,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW54" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX54" t="n">
         <v>0.09213674322672843</v>
@@ -32894,7 +32894,7 @@
         </is>
       </c>
       <c r="FB54" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC54" t="n">
         <v>0.1632296302323541</v>
@@ -32919,7 +32919,7 @@
         </is>
       </c>
       <c r="FI54" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ54" t="n">
         <v>100</v>
@@ -33058,7 +33058,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z55" t="n">
         <v>0.06614068918152717</v>
@@ -33094,7 +33094,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL55" t="n">
         <v>0.01637019174259785</v>
@@ -33130,7 +33130,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX55" t="n">
         <v>0.08171634449330044</v>
@@ -33184,7 +33184,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO55" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP55" t="n">
         <v>0.02511225080497755</v>
@@ -33229,7 +33229,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD55" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE55" t="n">
         <v>0.03787717275399195</v>
@@ -33244,7 +33244,7 @@
         <v>0</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ55" t="n">
         <v>20</v>
@@ -33364,7 +33364,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW55" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX55" t="n">
         <v>0.09213674322672843</v>
@@ -33459,7 +33459,7 @@
         </is>
       </c>
       <c r="FB55" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC55" t="n">
         <v>0.1632296302323541</v>
@@ -33484,7 +33484,7 @@
         </is>
       </c>
       <c r="FI55" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ55" t="n">
         <v>100</v>
@@ -33673,7 +33673,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z56" t="n">
         <v>0.06614068918152717</v>
@@ -33709,7 +33709,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL56" t="n">
         <v>0.01637019174259785</v>
@@ -33745,7 +33745,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX56" t="n">
         <v>0.08171634449330044</v>
@@ -33799,7 +33799,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO56" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP56" t="n">
         <v>0.02511225080497755</v>
@@ -33844,7 +33844,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD56" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE56" t="n">
         <v>0.03787717275399195</v>
@@ -33859,7 +33859,7 @@
         <v>0</v>
       </c>
       <c r="CI56" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ56" t="n">
         <v>20</v>
@@ -33979,7 +33979,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW56" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX56" t="n">
         <v>0.09213674322672843</v>
@@ -34074,7 +34074,7 @@
         </is>
       </c>
       <c r="FB56" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC56" t="n">
         <v>0.1632296302323541</v>
@@ -34099,7 +34099,7 @@
         </is>
       </c>
       <c r="FI56" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ56" t="n">
         <v>100</v>
@@ -34167,7 +34167,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2422405963216705</v>
+        <v>0.2446157937919437</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -34196,13 +34196,13 @@
         <v>0.7749999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>0.339740906422595</v>
+        <v>0.3647089275441405</v>
       </c>
       <c r="L57" t="n">
         <v>0.07639178405141835</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2672739598415609</v>
+        <v>0.2718215007967266</v>
       </c>
       <c r="N57" t="n">
         <v>113</v>
@@ -34238,7 +34238,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z57" t="n">
         <v>0.06614068918152717</v>
@@ -34274,7 +34274,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK57" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL57" t="n">
         <v>0.01637019174259785</v>
@@ -34310,7 +34310,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX57" t="n">
         <v>0.08171634449330044</v>
@@ -34364,7 +34364,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO57" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP57" t="n">
         <v>0.02511225080497755</v>
@@ -34409,7 +34409,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD57" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE57" t="n">
         <v>0.03787717275399195</v>
@@ -34424,7 +34424,7 @@
         <v>0</v>
       </c>
       <c r="CI57" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ57" t="n">
         <v>20</v>
@@ -34544,7 +34544,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW57" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX57" t="n">
         <v>0.09213674322672843</v>
@@ -34639,7 +34639,7 @@
         </is>
       </c>
       <c r="FB57" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC57" t="n">
         <v>0.1632296302323541</v>
@@ -34664,7 +34664,7 @@
         </is>
       </c>
       <c r="FI57" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ57" t="n">
         <v>100</v>
@@ -34803,7 +34803,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z58" t="n">
         <v>0.06614068918152717</v>
@@ -34839,7 +34839,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL58" t="n">
         <v>0.01637019174259785</v>
@@ -34875,7 +34875,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX58" t="n">
         <v>0.08171634449330044</v>
@@ -34929,7 +34929,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO58" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP58" t="n">
         <v>0.02511225080497755</v>
@@ -34974,7 +34974,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD58" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE58" t="n">
         <v>0.03787717275399195</v>
@@ -34989,7 +34989,7 @@
         <v>0</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ58" t="n">
         <v>20</v>
@@ -35109,7 +35109,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW58" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX58" t="n">
         <v>0.09213674322672843</v>
@@ -35204,7 +35204,7 @@
         </is>
       </c>
       <c r="FB58" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC58" t="n">
         <v>0.1632296302323541</v>
@@ -35229,7 +35229,7 @@
         </is>
       </c>
       <c r="FI58" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ58" t="n">
         <v>100</v>
@@ -35418,7 +35418,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z59" t="n">
         <v>0.06614068918152717</v>
@@ -35454,7 +35454,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK59" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL59" t="n">
         <v>0.01637019174259785</v>
@@ -35490,7 +35490,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX59" t="n">
         <v>0.08171634449330044</v>
@@ -35544,7 +35544,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO59" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP59" t="n">
         <v>0.02511225080497755</v>
@@ -35589,7 +35589,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD59" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE59" t="n">
         <v>0.03787717275399195</v>
@@ -35604,7 +35604,7 @@
         <v>0</v>
       </c>
       <c r="CI59" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ59" t="n">
         <v>20</v>
@@ -35724,7 +35724,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW59" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX59" t="n">
         <v>0.09213674322672843</v>
@@ -35819,7 +35819,7 @@
         </is>
       </c>
       <c r="FB59" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC59" t="n">
         <v>0.1632296302323541</v>
@@ -35844,7 +35844,7 @@
         </is>
       </c>
       <c r="FI59" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ59" t="n">
         <v>100</v>
@@ -36033,7 +36033,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z60" t="n">
         <v>0.06614068918152717</v>
@@ -36069,7 +36069,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK60" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL60" t="n">
         <v>0.01637019174259785</v>
@@ -36105,7 +36105,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX60" t="n">
         <v>0.08171634449330044</v>
@@ -36159,7 +36159,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO60" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP60" t="n">
         <v>0.02511225080497755</v>
@@ -36204,7 +36204,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD60" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE60" t="n">
         <v>0.03787717275399195</v>
@@ -36219,7 +36219,7 @@
         <v>0</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ60" t="n">
         <v>20</v>
@@ -36339,7 +36339,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW60" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX60" t="n">
         <v>0.09213674322672843</v>
@@ -36434,7 +36434,7 @@
         </is>
       </c>
       <c r="FB60" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC60" t="n">
         <v>0.1632296302323541</v>
@@ -36459,7 +36459,7 @@
         </is>
       </c>
       <c r="FI60" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ60" t="n">
         <v>100</v>
@@ -36598,7 +36598,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z61" t="n">
         <v>0.06614068918152717</v>
@@ -36634,7 +36634,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL61" t="n">
         <v>0.01637019174259785</v>
@@ -36670,7 +36670,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW61" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX61" t="n">
         <v>0.08171634449330044</v>
@@ -36724,7 +36724,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO61" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP61" t="n">
         <v>0.02511225080497755</v>
@@ -36769,7 +36769,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD61" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE61" t="n">
         <v>0.03787717275399195</v>
@@ -36784,7 +36784,7 @@
         <v>0</v>
       </c>
       <c r="CI61" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ61" t="n">
         <v>20</v>
@@ -36904,7 +36904,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW61" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX61" t="n">
         <v>0.09213674322672843</v>
@@ -36999,7 +36999,7 @@
         </is>
       </c>
       <c r="FB61" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC61" t="n">
         <v>0.1632296302323541</v>
@@ -37024,7 +37024,7 @@
         </is>
       </c>
       <c r="FI61" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ61" t="n">
         <v>100</v>
@@ -37213,7 +37213,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z62" t="n">
         <v>0.06614068918152717</v>
@@ -37249,7 +37249,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK62" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL62" t="n">
         <v>0.01637019174259785</v>
@@ -37285,7 +37285,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW62" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX62" t="n">
         <v>0.08171634449330044</v>
@@ -37339,7 +37339,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO62" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP62" t="n">
         <v>0.02511225080497755</v>
@@ -37384,7 +37384,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD62" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE62" t="n">
         <v>0.03787717275399195</v>
@@ -37399,7 +37399,7 @@
         <v>0</v>
       </c>
       <c r="CI62" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ62" t="n">
         <v>20</v>
@@ -37519,7 +37519,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW62" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX62" t="n">
         <v>0.09213674322672843</v>
@@ -37614,7 +37614,7 @@
         </is>
       </c>
       <c r="FB62" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC62" t="n">
         <v>0.1632296302323541</v>
@@ -37639,7 +37639,7 @@
         </is>
       </c>
       <c r="FI62" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ62" t="n">
         <v>100</v>
@@ -37828,7 +37828,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z63" t="n">
         <v>0.06614068918152717</v>
@@ -37864,7 +37864,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK63" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL63" t="n">
         <v>0.01637019174259785</v>
@@ -37900,7 +37900,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW63" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX63" t="n">
         <v>0.08171634449330044</v>
@@ -37954,7 +37954,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO63" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP63" t="n">
         <v>0.02511225080497755</v>
@@ -37999,7 +37999,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD63" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE63" t="n">
         <v>0.03787717275399195</v>
@@ -38014,7 +38014,7 @@
         <v>0</v>
       </c>
       <c r="CI63" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ63" t="n">
         <v>20</v>
@@ -38134,7 +38134,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW63" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX63" t="n">
         <v>0.09213674322672843</v>
@@ -38229,7 +38229,7 @@
         </is>
       </c>
       <c r="FB63" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC63" t="n">
         <v>0.1632296302323541</v>
@@ -38254,7 +38254,7 @@
         </is>
       </c>
       <c r="FI63" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ63" t="n">
         <v>100</v>
@@ -38443,7 +38443,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z64" t="n">
         <v>0.06614068918152717</v>
@@ -38479,7 +38479,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK64" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL64" t="n">
         <v>0.01637019174259785</v>
@@ -38515,7 +38515,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW64" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX64" t="n">
         <v>0.08171634449330044</v>
@@ -38569,7 +38569,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO64" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP64" t="n">
         <v>0.02511225080497755</v>
@@ -38614,7 +38614,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE64" t="n">
         <v>0.03787717275399195</v>
@@ -38629,7 +38629,7 @@
         <v>0</v>
       </c>
       <c r="CI64" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ64" t="n">
         <v>20</v>
@@ -38749,7 +38749,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW64" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX64" t="n">
         <v>0.09213674322672843</v>
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="FB64" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC64" t="n">
         <v>0.1632296302323541</v>
@@ -38869,7 +38869,7 @@
         </is>
       </c>
       <c r="FI64" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ64" t="n">
         <v>100</v>
@@ -39008,7 +39008,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z65" t="n">
         <v>0.06614068918152717</v>
@@ -39044,7 +39044,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK65" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL65" t="n">
         <v>0.01637019174259785</v>
@@ -39080,7 +39080,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW65" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX65" t="n">
         <v>0.08171634449330044</v>
@@ -39134,7 +39134,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO65" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP65" t="n">
         <v>0.02511225080497755</v>
@@ -39179,7 +39179,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE65" t="n">
         <v>0.03787717275399195</v>
@@ -39194,7 +39194,7 @@
         <v>0</v>
       </c>
       <c r="CI65" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ65" t="n">
         <v>20</v>
@@ -39314,7 +39314,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW65" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX65" t="n">
         <v>0.09213674322672843</v>
@@ -39409,7 +39409,7 @@
         </is>
       </c>
       <c r="FB65" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC65" t="n">
         <v>0.1632296302323541</v>
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="FI65" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ65" t="n">
         <v>100</v>
@@ -39623,7 +39623,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z66" t="n">
         <v>0.06614068918152717</v>
@@ -39659,7 +39659,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK66" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL66" t="n">
         <v>0.01637019174259785</v>
@@ -39695,7 +39695,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW66" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX66" t="n">
         <v>0.08171634449330044</v>
@@ -39749,7 +39749,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO66" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP66" t="n">
         <v>0.02511225080497755</v>
@@ -39794,7 +39794,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD66" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE66" t="n">
         <v>0.03787717275399195</v>
@@ -39809,7 +39809,7 @@
         <v>0</v>
       </c>
       <c r="CI66" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ66" t="n">
         <v>20</v>
@@ -39929,7 +39929,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW66" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX66" t="n">
         <v>0.09213674322672843</v>
@@ -40024,7 +40024,7 @@
         </is>
       </c>
       <c r="FB66" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC66" t="n">
         <v>0.1632296302323541</v>
@@ -40049,7 +40049,7 @@
         </is>
       </c>
       <c r="FI66" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ66" t="n">
         <v>100</v>
@@ -40188,7 +40188,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z67" t="n">
         <v>0.06614068918152717</v>
@@ -40224,7 +40224,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK67" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL67" t="n">
         <v>0.01637019174259785</v>
@@ -40260,7 +40260,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW67" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX67" t="n">
         <v>0.08171634449330044</v>
@@ -40314,7 +40314,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO67" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP67" t="n">
         <v>0.02511225080497755</v>
@@ -40359,7 +40359,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD67" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE67" t="n">
         <v>0.03787717275399195</v>
@@ -40374,7 +40374,7 @@
         <v>0</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ67" t="n">
         <v>20</v>
@@ -40494,7 +40494,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW67" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX67" t="n">
         <v>0.09213674322672843</v>
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="FB67" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC67" t="n">
         <v>0.1632296302323541</v>
@@ -40614,7 +40614,7 @@
         </is>
       </c>
       <c r="FI67" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ67" t="n">
         <v>100</v>
@@ -40803,7 +40803,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z68" t="n">
         <v>0.06614068918152717</v>
@@ -40839,7 +40839,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK68" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL68" t="n">
         <v>0.01637019174259785</v>
@@ -40875,7 +40875,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW68" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX68" t="n">
         <v>0.08171634449330044</v>
@@ -40929,7 +40929,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO68" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP68" t="n">
         <v>0.02511225080497755</v>
@@ -40974,7 +40974,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD68" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE68" t="n">
         <v>0.03787717275399195</v>
@@ -40989,7 +40989,7 @@
         <v>0</v>
       </c>
       <c r="CI68" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ68" t="n">
         <v>20</v>
@@ -41109,7 +41109,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW68" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX68" t="n">
         <v>0.09213674322672843</v>
@@ -41204,7 +41204,7 @@
         </is>
       </c>
       <c r="FB68" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC68" t="n">
         <v>0.1632296302323541</v>
@@ -41229,7 +41229,7 @@
         </is>
       </c>
       <c r="FI68" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ68" t="n">
         <v>100</v>
@@ -41368,7 +41368,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z69" t="n">
         <v>0.06614068918152717</v>
@@ -41404,7 +41404,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK69" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL69" t="n">
         <v>0.01637019174259785</v>
@@ -41440,7 +41440,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW69" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX69" t="n">
         <v>0.08171634449330044</v>
@@ -41494,7 +41494,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO69" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP69" t="n">
         <v>0.02511225080497755</v>
@@ -41539,7 +41539,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD69" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE69" t="n">
         <v>0.03787717275399195</v>
@@ -41554,7 +41554,7 @@
         <v>0</v>
       </c>
       <c r="CI69" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ69" t="n">
         <v>20</v>
@@ -41674,7 +41674,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW69" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX69" t="n">
         <v>0.09213674322672843</v>
@@ -41769,7 +41769,7 @@
         </is>
       </c>
       <c r="FB69" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC69" t="n">
         <v>0.1632296302323541</v>
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="FI69" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ69" t="n">
         <v>100</v>
@@ -41933,7 +41933,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z70" t="n">
         <v>0.06614068918152717</v>
@@ -41969,7 +41969,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK70" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL70" t="n">
         <v>0.01637019174259785</v>
@@ -42005,7 +42005,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW70" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX70" t="n">
         <v>0.08171634449330044</v>
@@ -42059,7 +42059,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO70" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP70" t="n">
         <v>0.02511225080497755</v>
@@ -42104,7 +42104,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD70" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE70" t="n">
         <v>0.03787717275399195</v>
@@ -42119,7 +42119,7 @@
         <v>0</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ70" t="n">
         <v>20</v>
@@ -42239,7 +42239,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW70" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX70" t="n">
         <v>0.09213674322672843</v>
@@ -42334,7 +42334,7 @@
         </is>
       </c>
       <c r="FB70" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC70" t="n">
         <v>0.1632296302323541</v>
@@ -42359,7 +42359,7 @@
         </is>
       </c>
       <c r="FI70" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ70" t="n">
         <v>100</v>
@@ -42498,7 +42498,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z71" t="n">
         <v>0.06614068918152717</v>
@@ -42534,7 +42534,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK71" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL71" t="n">
         <v>0.01637019174259785</v>
@@ -42570,7 +42570,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW71" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX71" t="n">
         <v>0.08171634449330044</v>
@@ -42624,7 +42624,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO71" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP71" t="n">
         <v>0.02511225080497755</v>
@@ -42669,7 +42669,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD71" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE71" t="n">
         <v>0.03787717275399195</v>
@@ -42684,7 +42684,7 @@
         <v>0</v>
       </c>
       <c r="CI71" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ71" t="n">
         <v>20</v>
@@ -42804,7 +42804,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW71" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX71" t="n">
         <v>0.09213674322672843</v>
@@ -42899,7 +42899,7 @@
         </is>
       </c>
       <c r="FB71" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC71" t="n">
         <v>0.1632296302323541</v>
@@ -42924,7 +42924,7 @@
         </is>
       </c>
       <c r="FI71" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ71" t="n">
         <v>100</v>
@@ -43109,7 +43109,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z72" t="n">
         <v>0.06614068918152717</v>
@@ -43145,7 +43145,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK72" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL72" t="n">
         <v>0.01637019174259785</v>
@@ -43181,7 +43181,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW72" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX72" t="n">
         <v>0.08171634449330044</v>
@@ -43235,7 +43235,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO72" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP72" t="n">
         <v>0.02511225080497755</v>
@@ -43280,7 +43280,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD72" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE72" t="n">
         <v>0.03787717275399195</v>
@@ -43295,7 +43295,7 @@
         <v>0</v>
       </c>
       <c r="CI72" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ72" t="n">
         <v>20</v>
@@ -43415,7 +43415,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW72" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX72" t="n">
         <v>0.09213674322672843</v>
@@ -43510,7 +43510,7 @@
         </is>
       </c>
       <c r="FB72" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC72" t="n">
         <v>0.1632296302323541</v>
@@ -43535,7 +43535,7 @@
         </is>
       </c>
       <c r="FI72" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ72" t="n">
         <v>100</v>
@@ -43674,7 +43674,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z73" t="n">
         <v>0.06614068918152717</v>
@@ -43710,7 +43710,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK73" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL73" t="n">
         <v>0.01637019174259785</v>
@@ -43746,7 +43746,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW73" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX73" t="n">
         <v>0.08171634449330044</v>
@@ -43800,7 +43800,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO73" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP73" t="n">
         <v>0.02511225080497755</v>
@@ -43845,7 +43845,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD73" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE73" t="n">
         <v>0.03787717275399195</v>
@@ -43860,7 +43860,7 @@
         <v>0</v>
       </c>
       <c r="CI73" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ73" t="n">
         <v>20</v>
@@ -43980,7 +43980,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW73" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX73" t="n">
         <v>0.09213674322672843</v>
@@ -44075,7 +44075,7 @@
         </is>
       </c>
       <c r="FB73" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC73" t="n">
         <v>0.1632296302323541</v>
@@ -44100,7 +44100,7 @@
         </is>
       </c>
       <c r="FI73" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ73" t="n">
         <v>100</v>
@@ -44289,7 +44289,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z74" t="n">
         <v>0.06614068918152717</v>
@@ -44325,7 +44325,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK74" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL74" t="n">
         <v>0.01637019174259785</v>
@@ -44361,7 +44361,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW74" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX74" t="n">
         <v>0.08171634449330044</v>
@@ -44415,7 +44415,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO74" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP74" t="n">
         <v>0.02511225080497755</v>
@@ -44460,7 +44460,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD74" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE74" t="n">
         <v>0.03787717275399195</v>
@@ -44475,7 +44475,7 @@
         <v>0</v>
       </c>
       <c r="CI74" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ74" t="n">
         <v>20</v>
@@ -44595,7 +44595,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW74" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX74" t="n">
         <v>0.09213674322672843</v>
@@ -44690,7 +44690,7 @@
         </is>
       </c>
       <c r="FB74" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC74" t="n">
         <v>0.1632296302323541</v>
@@ -44715,7 +44715,7 @@
         </is>
       </c>
       <c r="FI74" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ74" t="n">
         <v>100</v>
@@ -44854,7 +44854,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z75" t="n">
         <v>0.06614068918152717</v>
@@ -44890,7 +44890,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK75" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL75" t="n">
         <v>0.01637019174259785</v>
@@ -44926,7 +44926,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW75" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX75" t="n">
         <v>0.08171634449330044</v>
@@ -44980,7 +44980,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO75" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP75" t="n">
         <v>0.02511225080497755</v>
@@ -45025,7 +45025,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD75" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE75" t="n">
         <v>0.03787717275399195</v>
@@ -45040,7 +45040,7 @@
         <v>0</v>
       </c>
       <c r="CI75" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ75" t="n">
         <v>20</v>
@@ -45160,7 +45160,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW75" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX75" t="n">
         <v>0.09213674322672843</v>
@@ -45255,7 +45255,7 @@
         </is>
       </c>
       <c r="FB75" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC75" t="n">
         <v>0.1632296302323541</v>
@@ -45280,7 +45280,7 @@
         </is>
       </c>
       <c r="FI75" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ75" t="n">
         <v>100</v>
@@ -45419,7 +45419,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z76" t="n">
         <v>0.06614068918152717</v>
@@ -45455,7 +45455,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK76" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL76" t="n">
         <v>0.01637019174259785</v>
@@ -45491,7 +45491,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW76" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX76" t="n">
         <v>0.08171634449330044</v>
@@ -45545,7 +45545,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO76" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP76" t="n">
         <v>0.02511225080497755</v>
@@ -45590,7 +45590,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD76" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE76" t="n">
         <v>0.03787717275399195</v>
@@ -45605,7 +45605,7 @@
         <v>0</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ76" t="n">
         <v>20</v>
@@ -45725,7 +45725,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW76" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX76" t="n">
         <v>0.09213674322672843</v>
@@ -45820,7 +45820,7 @@
         </is>
       </c>
       <c r="FB76" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC76" t="n">
         <v>0.1632296302323541</v>
@@ -45845,7 +45845,7 @@
         </is>
       </c>
       <c r="FI76" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ76" t="n">
         <v>100</v>
@@ -45984,7 +45984,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z77" t="n">
         <v>0.06614068918152717</v>
@@ -46020,7 +46020,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK77" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL77" t="n">
         <v>0.01637019174259785</v>
@@ -46056,7 +46056,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW77" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX77" t="n">
         <v>0.08171634449330044</v>
@@ -46110,7 +46110,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO77" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP77" t="n">
         <v>0.02511225080497755</v>
@@ -46155,7 +46155,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD77" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE77" t="n">
         <v>0.03787717275399195</v>
@@ -46170,7 +46170,7 @@
         <v>0</v>
       </c>
       <c r="CI77" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ77" t="n">
         <v>20</v>
@@ -46290,7 +46290,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW77" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX77" t="n">
         <v>0.09213674322672843</v>
@@ -46385,7 +46385,7 @@
         </is>
       </c>
       <c r="FB77" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC77" t="n">
         <v>0.1632296302323541</v>
@@ -46410,7 +46410,7 @@
         </is>
       </c>
       <c r="FI77" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ77" t="n">
         <v>100</v>
@@ -46599,7 +46599,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z78" t="n">
         <v>0.06614068918152717</v>
@@ -46635,7 +46635,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK78" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL78" t="n">
         <v>0.01637019174259785</v>
@@ -46671,7 +46671,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW78" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX78" t="n">
         <v>0.08171634449330044</v>
@@ -46725,7 +46725,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO78" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP78" t="n">
         <v>0.02511225080497755</v>
@@ -46770,7 +46770,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD78" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE78" t="n">
         <v>0.03787717275399195</v>
@@ -46785,7 +46785,7 @@
         <v>0</v>
       </c>
       <c r="CI78" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ78" t="n">
         <v>20</v>
@@ -46905,7 +46905,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW78" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX78" t="n">
         <v>0.09213674322672843</v>
@@ -47000,7 +47000,7 @@
         </is>
       </c>
       <c r="FB78" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC78" t="n">
         <v>0.1632296302323541</v>
@@ -47025,7 +47025,7 @@
         </is>
       </c>
       <c r="FI78" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ78" t="n">
         <v>100</v>
@@ -47214,7 +47214,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z79" t="n">
         <v>0.06614068918152717</v>
@@ -47250,7 +47250,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK79" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL79" t="n">
         <v>0.01637019174259785</v>
@@ -47286,7 +47286,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW79" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX79" t="n">
         <v>0.08171634449330044</v>
@@ -47340,7 +47340,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO79" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP79" t="n">
         <v>0.02511225080497755</v>
@@ -47385,7 +47385,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE79" t="n">
         <v>0.03787717275399195</v>
@@ -47400,7 +47400,7 @@
         <v>0</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ79" t="n">
         <v>20</v>
@@ -47520,7 +47520,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW79" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX79" t="n">
         <v>0.09213674322672843</v>
@@ -47615,7 +47615,7 @@
         </is>
       </c>
       <c r="FB79" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC79" t="n">
         <v>0.1632296302323541</v>
@@ -47640,7 +47640,7 @@
         </is>
       </c>
       <c r="FI79" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ79" t="n">
         <v>100</v>
@@ -47829,7 +47829,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z80" t="n">
         <v>0.06614068918152717</v>
@@ -47865,7 +47865,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK80" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL80" t="n">
         <v>0.01637019174259785</v>
@@ -47901,7 +47901,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW80" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX80" t="n">
         <v>0.08171634449330044</v>
@@ -47955,7 +47955,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO80" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP80" t="n">
         <v>0.02511225080497755</v>
@@ -48000,7 +48000,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD80" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE80" t="n">
         <v>0.03787717275399195</v>
@@ -48015,7 +48015,7 @@
         <v>0</v>
       </c>
       <c r="CI80" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ80" t="n">
         <v>20</v>
@@ -48135,7 +48135,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW80" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX80" t="n">
         <v>0.09213674322672843</v>
@@ -48230,7 +48230,7 @@
         </is>
       </c>
       <c r="FB80" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC80" t="n">
         <v>0.1632296302323541</v>
@@ -48255,7 +48255,7 @@
         </is>
       </c>
       <c r="FI80" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ80" t="n">
         <v>100</v>
@@ -48394,7 +48394,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z81" t="n">
         <v>0.06614068918152717</v>
@@ -48430,7 +48430,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK81" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL81" t="n">
         <v>0.01637019174259785</v>
@@ -48466,7 +48466,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW81" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX81" t="n">
         <v>0.08171634449330044</v>
@@ -48520,7 +48520,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO81" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP81" t="n">
         <v>0.02511225080497755</v>
@@ -48565,7 +48565,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE81" t="n">
         <v>0.03787717275399195</v>
@@ -48580,7 +48580,7 @@
         <v>0</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ81" t="n">
         <v>20</v>
@@ -48700,7 +48700,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW81" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX81" t="n">
         <v>0.09213674322672843</v>
@@ -48795,7 +48795,7 @@
         </is>
       </c>
       <c r="FB81" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC81" t="n">
         <v>0.1632296302323541</v>
@@ -48820,7 +48820,7 @@
         </is>
       </c>
       <c r="FI81" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ81" t="n">
         <v>100</v>
@@ -49005,7 +49005,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z82" t="n">
         <v>0.06614068918152717</v>
@@ -49041,7 +49041,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK82" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL82" t="n">
         <v>0.01637019174259785</v>
@@ -49077,7 +49077,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW82" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX82" t="n">
         <v>0.08171634449330044</v>
@@ -49131,7 +49131,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO82" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP82" t="n">
         <v>0.02511225080497755</v>
@@ -49176,7 +49176,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE82" t="n">
         <v>0.03787717275399195</v>
@@ -49191,7 +49191,7 @@
         <v>0</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ82" t="n">
         <v>20</v>
@@ -49311,7 +49311,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW82" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX82" t="n">
         <v>0.09213674322672843</v>
@@ -49406,7 +49406,7 @@
         </is>
       </c>
       <c r="FB82" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC82" t="n">
         <v>0.1632296302323541</v>
@@ -49431,7 +49431,7 @@
         </is>
       </c>
       <c r="FI82" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ82" t="n">
         <v>100</v>
@@ -49620,7 +49620,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z83" t="n">
         <v>0.06614068918152717</v>
@@ -49656,7 +49656,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK83" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL83" t="n">
         <v>0.01637019174259785</v>
@@ -49692,7 +49692,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW83" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX83" t="n">
         <v>0.08171634449330044</v>
@@ -49746,7 +49746,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO83" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP83" t="n">
         <v>0.02511225080497755</v>
@@ -49791,7 +49791,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD83" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE83" t="n">
         <v>0.03787717275399195</v>
@@ -49806,7 +49806,7 @@
         <v>0</v>
       </c>
       <c r="CI83" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ83" t="n">
         <v>20</v>
@@ -49926,7 +49926,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW83" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX83" t="n">
         <v>0.09213674322672843</v>
@@ -50021,7 +50021,7 @@
         </is>
       </c>
       <c r="FB83" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC83" t="n">
         <v>0.1632296302323541</v>
@@ -50046,7 +50046,7 @@
         </is>
       </c>
       <c r="FI83" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ83" t="n">
         <v>100</v>
@@ -50185,7 +50185,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z84" t="n">
         <v>0.06614068918152717</v>
@@ -50221,7 +50221,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK84" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL84" t="n">
         <v>0.01637019174259785</v>
@@ -50257,7 +50257,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW84" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX84" t="n">
         <v>0.08171634449330044</v>
@@ -50311,7 +50311,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO84" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP84" t="n">
         <v>0.02511225080497755</v>
@@ -50356,7 +50356,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD84" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE84" t="n">
         <v>0.03787717275399195</v>
@@ -50371,7 +50371,7 @@
         <v>0</v>
       </c>
       <c r="CI84" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ84" t="n">
         <v>20</v>
@@ -50491,7 +50491,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW84" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX84" t="n">
         <v>0.09213674322672843</v>
@@ -50586,7 +50586,7 @@
         </is>
       </c>
       <c r="FB84" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC84" t="n">
         <v>0.1632296302323541</v>
@@ -50611,7 +50611,7 @@
         </is>
       </c>
       <c r="FI84" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ84" t="n">
         <v>100</v>
@@ -50750,7 +50750,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z85" t="n">
         <v>0.06614068918152717</v>
@@ -50786,7 +50786,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK85" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL85" t="n">
         <v>0.01637019174259785</v>
@@ -50822,7 +50822,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW85" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX85" t="n">
         <v>0.08171634449330044</v>
@@ -50876,7 +50876,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO85" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP85" t="n">
         <v>0.02511225080497755</v>
@@ -50921,7 +50921,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD85" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE85" t="n">
         <v>0.03787717275399195</v>
@@ -50936,7 +50936,7 @@
         <v>0</v>
       </c>
       <c r="CI85" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ85" t="n">
         <v>20</v>
@@ -51056,7 +51056,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW85" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX85" t="n">
         <v>0.09213674322672843</v>
@@ -51151,7 +51151,7 @@
         </is>
       </c>
       <c r="FB85" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC85" t="n">
         <v>0.1632296302323541</v>
@@ -51176,7 +51176,7 @@
         </is>
       </c>
       <c r="FI85" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ85" t="n">
         <v>100</v>
@@ -51365,7 +51365,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z86" t="n">
         <v>0.06614068918152717</v>
@@ -51401,7 +51401,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK86" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL86" t="n">
         <v>0.01637019174259785</v>
@@ -51437,7 +51437,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW86" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX86" t="n">
         <v>0.08171634449330044</v>
@@ -51491,7 +51491,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO86" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP86" t="n">
         <v>0.02511225080497755</v>
@@ -51536,7 +51536,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD86" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE86" t="n">
         <v>0.03787717275399195</v>
@@ -51551,7 +51551,7 @@
         <v>0</v>
       </c>
       <c r="CI86" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ86" t="n">
         <v>20</v>
@@ -51671,7 +51671,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW86" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX86" t="n">
         <v>0.09213674322672843</v>
@@ -51766,7 +51766,7 @@
         </is>
       </c>
       <c r="FB86" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC86" t="n">
         <v>0.1632296302323541</v>
@@ -51791,7 +51791,7 @@
         </is>
       </c>
       <c r="FI86" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ86" t="n">
         <v>100</v>
@@ -51930,7 +51930,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z87" t="n">
         <v>0.06614068918152717</v>
@@ -51966,7 +51966,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK87" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL87" t="n">
         <v>0.01637019174259785</v>
@@ -52002,7 +52002,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW87" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX87" t="n">
         <v>0.08171634449330044</v>
@@ -52056,7 +52056,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO87" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP87" t="n">
         <v>0.02511225080497755</v>
@@ -52101,7 +52101,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD87" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE87" t="n">
         <v>0.03787717275399195</v>
@@ -52116,7 +52116,7 @@
         <v>0</v>
       </c>
       <c r="CI87" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ87" t="n">
         <v>20</v>
@@ -52236,7 +52236,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW87" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX87" t="n">
         <v>0.09213674322672843</v>
@@ -52331,7 +52331,7 @@
         </is>
       </c>
       <c r="FB87" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC87" t="n">
         <v>0.1632296302323541</v>
@@ -52356,7 +52356,7 @@
         </is>
       </c>
       <c r="FI87" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ87" t="n">
         <v>100</v>
@@ -52545,7 +52545,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z88" t="n">
         <v>0.06614068918152717</v>
@@ -52581,7 +52581,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK88" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL88" t="n">
         <v>0.01637019174259785</v>
@@ -52617,7 +52617,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW88" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX88" t="n">
         <v>0.08171634449330044</v>
@@ -52671,7 +52671,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO88" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP88" t="n">
         <v>0.02511225080497755</v>
@@ -52716,7 +52716,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE88" t="n">
         <v>0.03787717275399195</v>
@@ -52731,7 +52731,7 @@
         <v>0</v>
       </c>
       <c r="CI88" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ88" t="n">
         <v>20</v>
@@ -52851,7 +52851,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW88" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX88" t="n">
         <v>0.09213674322672843</v>
@@ -52946,7 +52946,7 @@
         </is>
       </c>
       <c r="FB88" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC88" t="n">
         <v>0.1632296302323541</v>
@@ -52971,7 +52971,7 @@
         </is>
       </c>
       <c r="FI88" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ88" t="n">
         <v>100</v>
@@ -53110,7 +53110,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y89" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z89" t="n">
         <v>0.06614068918152717</v>
@@ -53146,7 +53146,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK89" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL89" t="n">
         <v>0.01637019174259785</v>
@@ -53182,7 +53182,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW89" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX89" t="n">
         <v>0.08171634449330044</v>
@@ -53236,7 +53236,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO89" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP89" t="n">
         <v>0.02511225080497755</v>
@@ -53281,7 +53281,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD89" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE89" t="n">
         <v>0.03787717275399195</v>
@@ -53296,7 +53296,7 @@
         <v>0</v>
       </c>
       <c r="CI89" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ89" t="n">
         <v>20</v>
@@ -53416,7 +53416,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW89" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX89" t="n">
         <v>0.09213674322672843</v>
@@ -53511,7 +53511,7 @@
         </is>
       </c>
       <c r="FB89" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC89" t="n">
         <v>0.1632296302323541</v>
@@ -53536,7 +53536,7 @@
         </is>
       </c>
       <c r="FI89" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ89" t="n">
         <v>100</v>
@@ -53725,7 +53725,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z90" t="n">
         <v>0.06614068918152717</v>
@@ -53761,7 +53761,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK90" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL90" t="n">
         <v>0.01637019174259785</v>
@@ -53797,7 +53797,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW90" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX90" t="n">
         <v>0.08171634449330044</v>
@@ -53851,7 +53851,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO90" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP90" t="n">
         <v>0.02511225080497755</v>
@@ -53896,7 +53896,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE90" t="n">
         <v>0.03787717275399195</v>
@@ -53911,7 +53911,7 @@
         <v>0</v>
       </c>
       <c r="CI90" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ90" t="n">
         <v>20</v>
@@ -54031,7 +54031,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW90" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX90" t="n">
         <v>0.09213674322672843</v>
@@ -54126,7 +54126,7 @@
         </is>
       </c>
       <c r="FB90" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC90" t="n">
         <v>0.1632296302323541</v>
@@ -54151,7 +54151,7 @@
         </is>
       </c>
       <c r="FI90" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ90" t="n">
         <v>100</v>
@@ -54340,7 +54340,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y91" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z91" t="n">
         <v>0.06614068918152717</v>
@@ -54376,7 +54376,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK91" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL91" t="n">
         <v>0.01637019174259785</v>
@@ -54412,7 +54412,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW91" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX91" t="n">
         <v>0.08171634449330044</v>
@@ -54466,7 +54466,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO91" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP91" t="n">
         <v>0.02511225080497755</v>
@@ -54511,7 +54511,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD91" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE91" t="n">
         <v>0.03787717275399195</v>
@@ -54526,7 +54526,7 @@
         <v>0</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ91" t="n">
         <v>20</v>
@@ -54646,7 +54646,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW91" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX91" t="n">
         <v>0.09213674322672843</v>
@@ -54741,7 +54741,7 @@
         </is>
       </c>
       <c r="FB91" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC91" t="n">
         <v>0.1632296302323541</v>
@@ -54766,7 +54766,7 @@
         </is>
       </c>
       <c r="FI91" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ91" t="n">
         <v>100</v>
@@ -54955,7 +54955,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z92" t="n">
         <v>0.06614068918152717</v>
@@ -54991,7 +54991,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK92" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL92" t="n">
         <v>0.01637019174259785</v>
@@ -55027,7 +55027,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW92" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX92" t="n">
         <v>0.08171634449330044</v>
@@ -55081,7 +55081,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO92" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP92" t="n">
         <v>0.02511225080497755</v>
@@ -55126,7 +55126,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD92" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE92" t="n">
         <v>0.03787717275399195</v>
@@ -55141,7 +55141,7 @@
         <v>0</v>
       </c>
       <c r="CI92" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ92" t="n">
         <v>20</v>
@@ -55261,7 +55261,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW92" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX92" t="n">
         <v>0.09213674322672843</v>
@@ -55356,7 +55356,7 @@
         </is>
       </c>
       <c r="FB92" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC92" t="n">
         <v>0.1632296302323541</v>
@@ -55381,7 +55381,7 @@
         </is>
       </c>
       <c r="FI92" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ92" t="n">
         <v>100</v>
@@ -55570,7 +55570,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z93" t="n">
         <v>0.06614068918152717</v>
@@ -55606,7 +55606,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK93" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL93" t="n">
         <v>0.01637019174259785</v>
@@ -55642,7 +55642,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW93" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX93" t="n">
         <v>0.08171634449330044</v>
@@ -55696,7 +55696,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO93" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP93" t="n">
         <v>0.02511225080497755</v>
@@ -55741,7 +55741,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD93" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE93" t="n">
         <v>0.03787717275399195</v>
@@ -55756,7 +55756,7 @@
         <v>0</v>
       </c>
       <c r="CI93" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ93" t="n">
         <v>20</v>
@@ -55876,7 +55876,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW93" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX93" t="n">
         <v>0.09213674322672843</v>
@@ -55971,7 +55971,7 @@
         </is>
       </c>
       <c r="FB93" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC93" t="n">
         <v>0.1632296302323541</v>
@@ -55996,7 +55996,7 @@
         </is>
       </c>
       <c r="FI93" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ93" t="n">
         <v>100</v>
@@ -56135,7 +56135,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z94" t="n">
         <v>0.06614068918152717</v>
@@ -56171,7 +56171,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK94" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL94" t="n">
         <v>0.01637019174259785</v>
@@ -56207,7 +56207,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW94" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX94" t="n">
         <v>0.08171634449330044</v>
@@ -56261,7 +56261,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO94" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP94" t="n">
         <v>0.02511225080497755</v>
@@ -56306,7 +56306,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD94" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE94" t="n">
         <v>0.03787717275399195</v>
@@ -56321,7 +56321,7 @@
         <v>0</v>
       </c>
       <c r="CI94" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ94" t="n">
         <v>20</v>
@@ -56441,7 +56441,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW94" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX94" t="n">
         <v>0.09213674322672843</v>
@@ -56536,7 +56536,7 @@
         </is>
       </c>
       <c r="FB94" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC94" t="n">
         <v>0.1632296302323541</v>
@@ -56561,7 +56561,7 @@
         </is>
       </c>
       <c r="FI94" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ94" t="n">
         <v>100</v>
@@ -56750,7 +56750,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z95" t="n">
         <v>0.06614068918152717</v>
@@ -56786,7 +56786,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK95" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL95" t="n">
         <v>0.01637019174259785</v>
@@ -56822,7 +56822,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW95" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX95" t="n">
         <v>0.08171634449330044</v>
@@ -56876,7 +56876,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO95" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP95" t="n">
         <v>0.02511225080497755</v>
@@ -56921,7 +56921,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD95" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE95" t="n">
         <v>0.03787717275399195</v>
@@ -56936,7 +56936,7 @@
         <v>0</v>
       </c>
       <c r="CI95" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ95" t="n">
         <v>20</v>
@@ -57056,7 +57056,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW95" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX95" t="n">
         <v>0.09213674322672843</v>
@@ -57151,7 +57151,7 @@
         </is>
       </c>
       <c r="FB95" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC95" t="n">
         <v>0.1632296302323541</v>
@@ -57176,7 +57176,7 @@
         </is>
       </c>
       <c r="FI95" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ95" t="n">
         <v>100</v>
@@ -57365,7 +57365,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z96" t="n">
         <v>0.06614068918152717</v>
@@ -57401,7 +57401,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK96" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL96" t="n">
         <v>0.01637019174259785</v>
@@ -57437,7 +57437,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW96" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX96" t="n">
         <v>0.08171634449330044</v>
@@ -57491,7 +57491,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO96" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP96" t="n">
         <v>0.02511225080497755</v>
@@ -57536,7 +57536,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD96" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE96" t="n">
         <v>0.03787717275399195</v>
@@ -57551,7 +57551,7 @@
         <v>0</v>
       </c>
       <c r="CI96" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ96" t="n">
         <v>20</v>
@@ -57671,7 +57671,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW96" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX96" t="n">
         <v>0.09213674322672843</v>
@@ -57766,7 +57766,7 @@
         </is>
       </c>
       <c r="FB96" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC96" t="n">
         <v>0.1632296302323541</v>
@@ -57791,7 +57791,7 @@
         </is>
       </c>
       <c r="FI96" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ96" t="n">
         <v>100</v>
@@ -57980,7 +57980,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z97" t="n">
         <v>0.06614068918152717</v>
@@ -58016,7 +58016,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK97" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL97" t="n">
         <v>0.01637019174259785</v>
@@ -58052,7 +58052,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW97" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX97" t="n">
         <v>0.08171634449330044</v>
@@ -58106,7 +58106,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO97" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP97" t="n">
         <v>0.02511225080497755</v>
@@ -58151,7 +58151,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD97" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE97" t="n">
         <v>0.03787717275399195</v>
@@ -58166,7 +58166,7 @@
         <v>0</v>
       </c>
       <c r="CI97" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ97" t="n">
         <v>20</v>
@@ -58286,7 +58286,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW97" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX97" t="n">
         <v>0.09213674322672843</v>
@@ -58381,7 +58381,7 @@
         </is>
       </c>
       <c r="FB97" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC97" t="n">
         <v>0.1632296302323541</v>
@@ -58406,7 +58406,7 @@
         </is>
       </c>
       <c r="FI97" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ97" t="n">
         <v>100</v>
@@ -58474,7 +58474,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7174889157660744</v>
+        <v>0.7102982000691678</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>0.9153816527369236</v>
       </c>
       <c r="F98" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7054004995893289</v>
       </c>
       <c r="G98" t="n">
         <v>0.1337240281536406</v>
@@ -58509,7 +58509,7 @@
         <v>0.9999999999999989</v>
       </c>
       <c r="M98" t="n">
-        <v>0.6934777274944203</v>
+        <v>0.6797104199177266</v>
       </c>
       <c r="N98" t="n">
         <v>113</v>
@@ -58545,7 +58545,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z98" t="n">
         <v>0.06614068918152717</v>
@@ -58581,7 +58581,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK98" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL98" t="n">
         <v>0.01637019174259785</v>
@@ -58617,7 +58617,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW98" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX98" t="n">
         <v>0.08171634449330044</v>
@@ -58671,7 +58671,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO98" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP98" t="n">
         <v>0.02511225080497755</v>
@@ -58716,7 +58716,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD98" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE98" t="n">
         <v>0.03787717275399195</v>
@@ -58731,7 +58731,7 @@
         <v>0</v>
       </c>
       <c r="CI98" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ98" t="n">
         <v>20</v>
@@ -58851,7 +58851,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW98" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX98" t="n">
         <v>0.09213674322672843</v>
@@ -58946,7 +58946,7 @@
         </is>
       </c>
       <c r="FB98" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC98" t="n">
         <v>0.1632296302323541</v>
@@ -58971,7 +58971,7 @@
         </is>
       </c>
       <c r="FI98" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ98" t="n">
         <v>100</v>
@@ -59110,7 +59110,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z99" t="n">
         <v>0.06614068918152717</v>
@@ -59146,7 +59146,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK99" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL99" t="n">
         <v>0.01637019174259785</v>
@@ -59182,7 +59182,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX99" t="n">
         <v>0.08171634449330044</v>
@@ -59236,7 +59236,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO99" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP99" t="n">
         <v>0.02511225080497755</v>
@@ -59281,7 +59281,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD99" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE99" t="n">
         <v>0.03787717275399195</v>
@@ -59296,7 +59296,7 @@
         <v>0</v>
       </c>
       <c r="CI99" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ99" t="n">
         <v>20</v>
@@ -59416,7 +59416,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW99" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX99" t="n">
         <v>0.09213674322672843</v>
@@ -59511,7 +59511,7 @@
         </is>
       </c>
       <c r="FB99" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC99" t="n">
         <v>0.1632296302323541</v>
@@ -59536,7 +59536,7 @@
         </is>
       </c>
       <c r="FI99" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ99" t="n">
         <v>100</v>
@@ -59675,7 +59675,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z100" t="n">
         <v>0.06614068918152717</v>
@@ -59711,7 +59711,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK100" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL100" t="n">
         <v>0.01637019174259785</v>
@@ -59747,7 +59747,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX100" t="n">
         <v>0.08171634449330044</v>
@@ -59801,7 +59801,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO100" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP100" t="n">
         <v>0.02511225080497755</v>
@@ -59846,7 +59846,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD100" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE100" t="n">
         <v>0.03787717275399195</v>
@@ -59861,7 +59861,7 @@
         <v>0</v>
       </c>
       <c r="CI100" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ100" t="n">
         <v>20</v>
@@ -59981,7 +59981,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW100" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX100" t="n">
         <v>0.09213674322672843</v>
@@ -60076,7 +60076,7 @@
         </is>
       </c>
       <c r="FB100" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC100" t="n">
         <v>0.1632296302323541</v>
@@ -60101,7 +60101,7 @@
         </is>
       </c>
       <c r="FI100" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ100" t="n">
         <v>100</v>
@@ -60240,7 +60240,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z101" t="n">
         <v>0.06614068918152717</v>
@@ -60276,7 +60276,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK101" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL101" t="n">
         <v>0.01637019174259785</v>
@@ -60312,7 +60312,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX101" t="n">
         <v>0.08171634449330044</v>
@@ -60366,7 +60366,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO101" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP101" t="n">
         <v>0.02511225080497755</v>
@@ -60411,7 +60411,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD101" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE101" t="n">
         <v>0.03787717275399195</v>
@@ -60426,7 +60426,7 @@
         <v>0</v>
       </c>
       <c r="CI101" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ101" t="n">
         <v>20</v>
@@ -60546,7 +60546,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW101" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX101" t="n">
         <v>0.09213674322672843</v>
@@ -60641,7 +60641,7 @@
         </is>
       </c>
       <c r="FB101" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC101" t="n">
         <v>0.1632296302323541</v>
@@ -60666,7 +60666,7 @@
         </is>
       </c>
       <c r="FI101" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ101" t="n">
         <v>100</v>
@@ -60855,7 +60855,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z102" t="n">
         <v>0.06614068918152717</v>
@@ -60891,7 +60891,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK102" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL102" t="n">
         <v>0.01637019174259785</v>
@@ -60927,7 +60927,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX102" t="n">
         <v>0.08171634449330044</v>
@@ -60981,7 +60981,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO102" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP102" t="n">
         <v>0.02511225080497755</v>
@@ -61026,7 +61026,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD102" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE102" t="n">
         <v>0.03787717275399195</v>
@@ -61041,7 +61041,7 @@
         <v>0</v>
       </c>
       <c r="CI102" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ102" t="n">
         <v>20</v>
@@ -61161,7 +61161,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW102" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX102" t="n">
         <v>0.09213674322672843</v>
@@ -61256,7 +61256,7 @@
         </is>
       </c>
       <c r="FB102" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC102" t="n">
         <v>0.1632296302323541</v>
@@ -61281,7 +61281,7 @@
         </is>
       </c>
       <c r="FI102" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ102" t="n">
         <v>100</v>
@@ -61470,7 +61470,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z103" t="n">
         <v>0.06614068918152717</v>
@@ -61506,7 +61506,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK103" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL103" t="n">
         <v>0.01637019174259785</v>
@@ -61542,7 +61542,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW103" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX103" t="n">
         <v>0.08171634449330044</v>
@@ -61596,7 +61596,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO103" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP103" t="n">
         <v>0.02511225080497755</v>
@@ -61641,7 +61641,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD103" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE103" t="n">
         <v>0.03787717275399195</v>
@@ -61656,7 +61656,7 @@
         <v>0</v>
       </c>
       <c r="CI103" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ103" t="n">
         <v>20</v>
@@ -61776,7 +61776,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW103" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX103" t="n">
         <v>0.09213674322672843</v>
@@ -61871,7 +61871,7 @@
         </is>
       </c>
       <c r="FB103" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC103" t="n">
         <v>0.1632296302323541</v>
@@ -61896,7 +61896,7 @@
         </is>
       </c>
       <c r="FI103" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ103" t="n">
         <v>100</v>
@@ -62085,7 +62085,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z104" t="n">
         <v>0.06614068918152717</v>
@@ -62121,7 +62121,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK104" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL104" t="n">
         <v>0.01637019174259785</v>
@@ -62157,7 +62157,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW104" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX104" t="n">
         <v>0.08171634449330044</v>
@@ -62211,7 +62211,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO104" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP104" t="n">
         <v>0.02511225080497755</v>
@@ -62256,7 +62256,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD104" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE104" t="n">
         <v>0.03787717275399195</v>
@@ -62271,7 +62271,7 @@
         <v>0</v>
       </c>
       <c r="CI104" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ104" t="n">
         <v>20</v>
@@ -62391,7 +62391,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW104" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX104" t="n">
         <v>0.09213674322672843</v>
@@ -62486,7 +62486,7 @@
         </is>
       </c>
       <c r="FB104" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC104" t="n">
         <v>0.1632296302323541</v>
@@ -62511,7 +62511,7 @@
         </is>
       </c>
       <c r="FI104" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ104" t="n">
         <v>100</v>
@@ -62700,7 +62700,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z105" t="n">
         <v>0.06614068918152717</v>
@@ -62736,7 +62736,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK105" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL105" t="n">
         <v>0.01637019174259785</v>
@@ -62772,7 +62772,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW105" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX105" t="n">
         <v>0.08171634449330044</v>
@@ -62826,7 +62826,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO105" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP105" t="n">
         <v>0.02511225080497755</v>
@@ -62871,7 +62871,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD105" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE105" t="n">
         <v>0.03787717275399195</v>
@@ -62886,7 +62886,7 @@
         <v>0</v>
       </c>
       <c r="CI105" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ105" t="n">
         <v>20</v>
@@ -63006,7 +63006,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW105" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX105" t="n">
         <v>0.09213674322672843</v>
@@ -63101,7 +63101,7 @@
         </is>
       </c>
       <c r="FB105" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC105" t="n">
         <v>0.1632296302323541</v>
@@ -63126,7 +63126,7 @@
         </is>
       </c>
       <c r="FI105" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ105" t="n">
         <v>100</v>
@@ -63315,7 +63315,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y106" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z106" t="n">
         <v>0.06614068918152717</v>
@@ -63351,7 +63351,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK106" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL106" t="n">
         <v>0.01637019174259785</v>
@@ -63387,7 +63387,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW106" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX106" t="n">
         <v>0.08171634449330044</v>
@@ -63441,7 +63441,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO106" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP106" t="n">
         <v>0.02511225080497755</v>
@@ -63486,7 +63486,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD106" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE106" t="n">
         <v>0.03787717275399195</v>
@@ -63501,7 +63501,7 @@
         <v>0</v>
       </c>
       <c r="CI106" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ106" t="n">
         <v>20</v>
@@ -63621,7 +63621,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW106" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX106" t="n">
         <v>0.09213674322672843</v>
@@ -63716,7 +63716,7 @@
         </is>
       </c>
       <c r="FB106" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC106" t="n">
         <v>0.1632296302323541</v>
@@ -63741,7 +63741,7 @@
         </is>
       </c>
       <c r="FI106" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ106" t="n">
         <v>100</v>
@@ -63930,7 +63930,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y107" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z107" t="n">
         <v>0.06614068918152717</v>
@@ -63966,7 +63966,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK107" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL107" t="n">
         <v>0.01637019174259785</v>
@@ -64002,7 +64002,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW107" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX107" t="n">
         <v>0.08171634449330044</v>
@@ -64056,7 +64056,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO107" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP107" t="n">
         <v>0.02511225080497755</v>
@@ -64101,7 +64101,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD107" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE107" t="n">
         <v>0.03787717275399195</v>
@@ -64116,7 +64116,7 @@
         <v>0</v>
       </c>
       <c r="CI107" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ107" t="n">
         <v>20</v>
@@ -64236,7 +64236,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW107" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX107" t="n">
         <v>0.09213674322672843</v>
@@ -64331,7 +64331,7 @@
         </is>
       </c>
       <c r="FB107" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC107" t="n">
         <v>0.1632296302323541</v>
@@ -64356,7 +64356,7 @@
         </is>
       </c>
       <c r="FI107" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ107" t="n">
         <v>100</v>
@@ -64545,7 +64545,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y108" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z108" t="n">
         <v>0.06614068918152717</v>
@@ -64581,7 +64581,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK108" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL108" t="n">
         <v>0.01637019174259785</v>
@@ -64617,7 +64617,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW108" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX108" t="n">
         <v>0.08171634449330044</v>
@@ -64671,7 +64671,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO108" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP108" t="n">
         <v>0.02511225080497755</v>
@@ -64716,7 +64716,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD108" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE108" t="n">
         <v>0.03787717275399195</v>
@@ -64731,7 +64731,7 @@
         <v>0</v>
       </c>
       <c r="CI108" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ108" t="n">
         <v>20</v>
@@ -64851,7 +64851,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW108" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX108" t="n">
         <v>0.09213674322672843</v>
@@ -64946,7 +64946,7 @@
         </is>
       </c>
       <c r="FB108" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC108" t="n">
         <v>0.1632296302323541</v>
@@ -64971,7 +64971,7 @@
         </is>
       </c>
       <c r="FI108" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ108" t="n">
         <v>100</v>
@@ -65110,7 +65110,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y109" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z109" t="n">
         <v>0.06614068918152717</v>
@@ -65146,7 +65146,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK109" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL109" t="n">
         <v>0.01637019174259785</v>
@@ -65182,7 +65182,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW109" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX109" t="n">
         <v>0.08171634449330044</v>
@@ -65236,7 +65236,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO109" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP109" t="n">
         <v>0.02511225080497755</v>
@@ -65281,7 +65281,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD109" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE109" t="n">
         <v>0.03787717275399195</v>
@@ -65296,7 +65296,7 @@
         <v>0</v>
       </c>
       <c r="CI109" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ109" t="n">
         <v>20</v>
@@ -65416,7 +65416,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW109" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX109" t="n">
         <v>0.09213674322672843</v>
@@ -65511,7 +65511,7 @@
         </is>
       </c>
       <c r="FB109" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC109" t="n">
         <v>0.1632296302323541</v>
@@ -65536,7 +65536,7 @@
         </is>
       </c>
       <c r="FI109" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ109" t="n">
         <v>100</v>
@@ -65725,7 +65725,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y110" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z110" t="n">
         <v>0.06614068918152717</v>
@@ -65761,7 +65761,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK110" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL110" t="n">
         <v>0.01637019174259785</v>
@@ -65797,7 +65797,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW110" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX110" t="n">
         <v>0.08171634449330044</v>
@@ -65851,7 +65851,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO110" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP110" t="n">
         <v>0.02511225080497755</v>
@@ -65896,7 +65896,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD110" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE110" t="n">
         <v>0.03787717275399195</v>
@@ -65911,7 +65911,7 @@
         <v>0</v>
       </c>
       <c r="CI110" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ110" t="n">
         <v>20</v>
@@ -66031,7 +66031,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW110" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX110" t="n">
         <v>0.09213674322672843</v>
@@ -66126,7 +66126,7 @@
         </is>
       </c>
       <c r="FB110" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC110" t="n">
         <v>0.1632296302323541</v>
@@ -66151,7 +66151,7 @@
         </is>
       </c>
       <c r="FI110" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ110" t="n">
         <v>100</v>
@@ -66290,7 +66290,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y111" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z111" t="n">
         <v>0.06614068918152717</v>
@@ -66326,7 +66326,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK111" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL111" t="n">
         <v>0.01637019174259785</v>
@@ -66362,7 +66362,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW111" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX111" t="n">
         <v>0.08171634449330044</v>
@@ -66416,7 +66416,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO111" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP111" t="n">
         <v>0.02511225080497755</v>
@@ -66461,7 +66461,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD111" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE111" t="n">
         <v>0.03787717275399195</v>
@@ -66476,7 +66476,7 @@
         <v>0</v>
       </c>
       <c r="CI111" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ111" t="n">
         <v>20</v>
@@ -66596,7 +66596,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW111" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX111" t="n">
         <v>0.09213674322672843</v>
@@ -66691,7 +66691,7 @@
         </is>
       </c>
       <c r="FB111" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC111" t="n">
         <v>0.1632296302323541</v>
@@ -66716,7 +66716,7 @@
         </is>
       </c>
       <c r="FI111" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ111" t="n">
         <v>100</v>
@@ -66905,7 +66905,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y112" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z112" t="n">
         <v>0.06614068918152717</v>
@@ -66941,7 +66941,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK112" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL112" t="n">
         <v>0.01637019174259785</v>
@@ -66977,7 +66977,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX112" t="n">
         <v>0.08171634449330044</v>
@@ -67031,7 +67031,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO112" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP112" t="n">
         <v>0.02511225080497755</v>
@@ -67076,7 +67076,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD112" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE112" t="n">
         <v>0.03787717275399195</v>
@@ -67091,7 +67091,7 @@
         <v>0</v>
       </c>
       <c r="CI112" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ112" t="n">
         <v>20</v>
@@ -67211,7 +67211,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW112" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX112" t="n">
         <v>0.09213674322672843</v>
@@ -67306,7 +67306,7 @@
         </is>
       </c>
       <c r="FB112" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC112" t="n">
         <v>0.1632296302323541</v>
@@ -67331,7 +67331,7 @@
         </is>
       </c>
       <c r="FI112" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ112" t="n">
         <v>100</v>
@@ -67449,7 +67449,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4543064625116398</v>
+        <v>0.4610863323227429</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -67460,7 +67460,7 @@
         <v>0.4331568546537495</v>
       </c>
       <c r="E113" t="n">
-        <v>0.6173091736315381</v>
+        <v>0.7019275208946145</v>
       </c>
       <c r="F113" t="n">
         <v>0.2392146296411173</v>
@@ -67484,7 +67484,7 @@
         <v>0.3382302099500095</v>
       </c>
       <c r="M113" t="n">
-        <v>0.473649785925013</v>
+        <v>0.4866304900654301</v>
       </c>
       <c r="N113" t="n">
         <v>113</v>
@@ -67520,7 +67520,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y113" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z113" t="n">
         <v>0.06614068918152717</v>
@@ -67556,7 +67556,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK113" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL113" t="n">
         <v>0.01637019174259785</v>
@@ -67592,7 +67592,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX113" t="n">
         <v>0.08171634449330044</v>
@@ -67646,7 +67646,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO113" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP113" t="n">
         <v>0.02511225080497755</v>
@@ -67691,7 +67691,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD113" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE113" t="n">
         <v>0.03787717275399195</v>
@@ -67706,7 +67706,7 @@
         <v>0</v>
       </c>
       <c r="CI113" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ113" t="n">
         <v>20</v>
@@ -67826,7 +67826,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW113" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX113" t="n">
         <v>0.09213674322672843</v>
@@ -67921,7 +67921,7 @@
         </is>
       </c>
       <c r="FB113" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC113" t="n">
         <v>0.1632296302323541</v>
@@ -67946,7 +67946,7 @@
         </is>
       </c>
       <c r="FI113" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ113" t="n">
         <v>100</v>
@@ -68018,10 +68018,10 @@
         <v>0.553945959583809</v>
       </c>
       <c r="GC113" t="n">
-        <v>0.4034908296573994</v>
+        <v>0.417536073251657</v>
       </c>
       <c r="GD113" t="n">
-        <v>-0.1504551299264096</v>
+        <v>-0.136409886332152</v>
       </c>
       <c r="GE113" t="inlineStr">
         <is>
@@ -68041,10 +68041,10 @@
         <v>0.6739533658513143</v>
       </c>
       <c r="GJ113" t="n">
-        <v>0.3379562854650782</v>
+        <v>0.3660467726535935</v>
       </c>
       <c r="GK113" t="n">
-        <v>-0.335997080386236</v>
+        <v>-0.3079065931977208</v>
       </c>
       <c r="GL113" t="inlineStr">
         <is>
@@ -68135,7 +68135,7 @@
         <v>87.61061946902655</v>
       </c>
       <c r="Y114" t="n">
-        <v>0.1876921417664673</v>
+        <v>0.1878708596449244</v>
       </c>
       <c r="Z114" t="n">
         <v>0.06614068918152717</v>
@@ -68171,7 +68171,7 @@
         <v>12.38938053097345</v>
       </c>
       <c r="AK114" t="n">
-        <v>0.1629976742392745</v>
+        <v>0.1632713155958371</v>
       </c>
       <c r="AL114" t="n">
         <v>0.01637019174259785</v>
@@ -68207,7 +68207,7 @@
         <v>13.27433628318584</v>
       </c>
       <c r="AW114" t="n">
-        <v>0.2102775757427919</v>
+        <v>0.2103694770925995</v>
       </c>
       <c r="AX114" t="n">
         <v>0.08171634449330044</v>
@@ -68261,7 +68261,7 @@
         <v>4.424778761061947</v>
       </c>
       <c r="BO114" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="BP114" t="n">
         <v>0.02511225080497755</v>
@@ -68306,7 +68306,7 @@
         <v>23.89380530973451</v>
       </c>
       <c r="CD114" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="CE114" t="n">
         <v>0.03787717275399195</v>
@@ -68321,7 +68321,7 @@
         <v>0</v>
       </c>
       <c r="CI114" t="n">
-        <v>0.7797517428070392</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="CJ114" t="n">
         <v>20</v>
@@ -68441,7 +68441,7 @@
         <v>30.97345132743363</v>
       </c>
       <c r="DW114" t="n">
-        <v>0.2040864761932477</v>
+        <v>0.2043074321323765</v>
       </c>
       <c r="DX114" t="n">
         <v>0.09213674322672843</v>
@@ -68536,7 +68536,7 @@
         </is>
       </c>
       <c r="FB114" t="n">
-        <v>0.3063840415876833</v>
+        <v>0.3071328765192149</v>
       </c>
       <c r="FC114" t="n">
         <v>0.1632296302323541</v>
@@ -68561,7 +68561,7 @@
         </is>
       </c>
       <c r="FI114" t="n">
-        <v>0.1507167588584819</v>
+        <v>0.1503753574616771</v>
       </c>
       <c r="FJ114" t="n">
         <v>100</v>
